--- a/Spreadsheets/Opponent_Tracker.xlsx
+++ b/Spreadsheets/Opponent_Tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CACABE78-0519-4D16-9DA4-C8BA82683671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FDD5FE-BEB5-4517-971D-9C9269848DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14715" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="opponents_table" sheetId="1" r:id="rId1"/>
@@ -3616,24 +3616,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3650,6 +3632,77 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3658,6 +3711,73 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3690,129 +3810,9 @@
     <xf numFmtId="0" fontId="3" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 3" xfId="1" builtinId="18"/>
@@ -4198,7 +4198,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:BN140"/>
+  <dimension ref="A1:BN161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.7109375" customWidth="1"/>
@@ -4236,96 +4236,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="168" t="s">
+      <c r="G1" s="182" t="s">
         <v>771</v>
       </c>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="145" t="s">
+      <c r="H1" s="183"/>
+      <c r="I1" s="183"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="197" t="s">
         <v>770</v>
       </c>
-      <c r="L1" s="146"/>
-      <c r="M1" s="146"/>
-      <c r="N1" s="147"/>
-      <c r="O1" s="157" t="s">
+      <c r="L1" s="198"/>
+      <c r="M1" s="198"/>
+      <c r="N1" s="199"/>
+      <c r="O1" s="172" t="s">
         <v>769</v>
       </c>
-      <c r="P1" s="158"/>
-      <c r="Q1" s="158"/>
-      <c r="R1" s="159"/>
-      <c r="S1" s="148" t="s">
+      <c r="P1" s="173"/>
+      <c r="Q1" s="173"/>
+      <c r="R1" s="174"/>
+      <c r="S1" s="200" t="s">
         <v>768</v>
       </c>
-      <c r="T1" s="149"/>
-      <c r="U1" s="149"/>
-      <c r="V1" s="150"/>
-      <c r="W1" s="173" t="s">
+      <c r="T1" s="201"/>
+      <c r="U1" s="201"/>
+      <c r="V1" s="202"/>
+      <c r="W1" s="139" t="s">
         <v>765</v>
       </c>
-      <c r="X1" s="174"/>
-      <c r="Y1" s="175"/>
-      <c r="Z1" s="176"/>
-      <c r="AA1" s="200" t="s">
+      <c r="X1" s="140"/>
+      <c r="Y1" s="141"/>
+      <c r="Z1" s="142"/>
+      <c r="AA1" s="131" t="s">
         <v>766</v>
       </c>
-      <c r="AB1" s="201"/>
-      <c r="AC1" s="202"/>
-      <c r="AD1" s="203"/>
-      <c r="AE1" s="196" t="s">
+      <c r="AB1" s="132"/>
+      <c r="AC1" s="133"/>
+      <c r="AD1" s="134"/>
+      <c r="AE1" s="127" t="s">
         <v>767</v>
       </c>
-      <c r="AF1" s="197"/>
-      <c r="AG1" s="198"/>
-      <c r="AH1" s="199"/>
-      <c r="AI1" s="163" t="s">
+      <c r="AF1" s="128"/>
+      <c r="AG1" s="129"/>
+      <c r="AH1" s="130"/>
+      <c r="AI1" s="176" t="s">
         <v>858</v>
       </c>
-      <c r="AJ1" s="164"/>
-      <c r="AK1" s="165"/>
-      <c r="AL1" s="166"/>
-      <c r="AM1" s="127" t="s">
+      <c r="AJ1" s="177"/>
+      <c r="AK1" s="178"/>
+      <c r="AL1" s="179"/>
+      <c r="AM1" s="119" t="s">
         <v>859</v>
       </c>
-      <c r="AN1" s="128"/>
-      <c r="AO1" s="129"/>
-      <c r="AP1" s="130"/>
-      <c r="AQ1" s="127" t="s">
+      <c r="AN1" s="120"/>
+      <c r="AO1" s="121"/>
+      <c r="AP1" s="122"/>
+      <c r="AQ1" s="119" t="s">
         <v>860</v>
       </c>
-      <c r="AR1" s="128"/>
-      <c r="AS1" s="129"/>
-      <c r="AT1" s="130"/>
-      <c r="AU1" s="127" t="s">
+      <c r="AR1" s="120"/>
+      <c r="AS1" s="121"/>
+      <c r="AT1" s="122"/>
+      <c r="AU1" s="119" t="s">
         <v>861</v>
       </c>
-      <c r="AV1" s="128"/>
-      <c r="AW1" s="129"/>
-      <c r="AX1" s="130"/>
-      <c r="AY1" s="127" t="s">
+      <c r="AV1" s="120"/>
+      <c r="AW1" s="121"/>
+      <c r="AX1" s="122"/>
+      <c r="AY1" s="119" t="s">
         <v>862</v>
       </c>
-      <c r="AZ1" s="128"/>
-      <c r="BA1" s="129"/>
-      <c r="BB1" s="130"/>
-      <c r="BC1" s="127" t="s">
+      <c r="AZ1" s="120"/>
+      <c r="BA1" s="121"/>
+      <c r="BB1" s="122"/>
+      <c r="BC1" s="119" t="s">
         <v>829</v>
       </c>
-      <c r="BD1" s="128"/>
-      <c r="BE1" s="129"/>
-      <c r="BF1" s="130"/>
-      <c r="BG1" s="127" t="s">
+      <c r="BD1" s="120"/>
+      <c r="BE1" s="121"/>
+      <c r="BF1" s="122"/>
+      <c r="BG1" s="119" t="s">
         <v>830</v>
       </c>
-      <c r="BH1" s="128"/>
-      <c r="BI1" s="129"/>
-      <c r="BJ1" s="130"/>
-      <c r="BK1" s="127" t="s">
+      <c r="BH1" s="120"/>
+      <c r="BI1" s="121"/>
+      <c r="BJ1" s="122"/>
+      <c r="BK1" s="119" t="s">
         <v>831</v>
       </c>
-      <c r="BL1" s="128"/>
-      <c r="BM1" s="129"/>
-      <c r="BN1" s="130"/>
+      <c r="BL1" s="120"/>
+      <c r="BM1" s="121"/>
+      <c r="BN1" s="122"/>
     </row>
     <row r="2" spans="1:66" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="39" t="s">
@@ -4510,15 +4510,15 @@
       </c>
     </row>
     <row r="3" spans="1:66" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="167" t="s">
+      <c r="B3" s="180" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="12"/>
-      <c r="D3" s="191" t="s">
+      <c r="D3" s="159" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="126"/>
-      <c r="F3" s="152"/>
+      <c r="E3" s="148"/>
+      <c r="F3" s="149"/>
       <c r="G3" s="40">
         <f t="shared" ref="G3:AP3" si="0">COUNTIF(G11:G58,"✅")</f>
         <v>5</v>
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="126"/>
+      <c r="B4" s="148"/>
       <c r="C4" s="13"/>
-      <c r="D4" s="191" t="s">
+      <c r="D4" s="159" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="126"/>
-      <c r="F4" s="152"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="149"/>
       <c r="G4" s="40">
         <f t="shared" ref="G4:AP4" si="3">COUNTIF(G11:G58,"✅")+COUNTIF(G11:G58,"✔️")</f>
         <v>5</v>
@@ -5048,15 +5048,15 @@
       <c r="BJ5" s="52"/>
     </row>
     <row r="6" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="182" t="s">
+      <c r="B6" s="150" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="14"/>
-      <c r="D6" s="151" t="s">
+      <c r="D6" s="181" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="126"/>
-      <c r="F6" s="152"/>
+      <c r="E6" s="148"/>
+      <c r="F6" s="149"/>
       <c r="G6" s="43">
         <v>0</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="AM6" s="86">
-        <f>COUNTIF(AM60:AM131,"✅")</f>
+        <f>COUNTIF(AM60:AM152,"✅")</f>
         <v>2</v>
       </c>
       <c r="AN6" s="88">
@@ -5232,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="BC6" s="86">
-        <f>COUNTIF(BC60:BC121,"✅")</f>
+        <f>COUNTIF(BC60:BC142,"✅")</f>
         <v>0</v>
       </c>
       <c r="BD6" s="88">
@@ -5248,7 +5248,7 @@
         <v>0</v>
       </c>
       <c r="BG6" s="86">
-        <f>COUNTIF(BG60:BG127,"✅")</f>
+        <f>COUNTIF(BG60:BG148,"✅")</f>
         <v>0</v>
       </c>
       <c r="BH6" s="88">
@@ -5281,13 +5281,13 @@
       </c>
     </row>
     <row r="7" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="126"/>
+      <c r="B7" s="148"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="151" t="s">
+      <c r="D7" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="126"/>
-      <c r="F7" s="152"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="149"/>
       <c r="G7" s="43">
         <v>0</v>
       </c>
@@ -5512,258 +5512,258 @@
       </c>
     </row>
     <row r="8" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="D8" s="181" t="s">
+      <c r="D8" s="147" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="126"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="153">
+      <c r="E8" s="148"/>
+      <c r="F8" s="149"/>
+      <c r="G8" s="168">
         <f>SUM(G3:J3)</f>
         <v>9</v>
       </c>
-      <c r="H8" s="154"/>
-      <c r="I8" s="155"/>
-      <c r="J8" s="156"/>
-      <c r="K8" s="139">
+      <c r="H8" s="169"/>
+      <c r="I8" s="170"/>
+      <c r="J8" s="171"/>
+      <c r="K8" s="191">
         <f>SUM(K3:N3)</f>
         <v>14</v>
       </c>
-      <c r="L8" s="140"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="142"/>
-      <c r="O8" s="177">
+      <c r="L8" s="192"/>
+      <c r="M8" s="193"/>
+      <c r="N8" s="194"/>
+      <c r="O8" s="143">
         <f>SUM(O3:R3)</f>
         <v>14</v>
       </c>
-      <c r="P8" s="178"/>
-      <c r="Q8" s="179"/>
-      <c r="R8" s="180"/>
-      <c r="S8" s="187">
+      <c r="P8" s="144"/>
+      <c r="Q8" s="145"/>
+      <c r="R8" s="146"/>
+      <c r="S8" s="155">
         <f>SUM(S3:V3)</f>
         <v>9</v>
       </c>
-      <c r="T8" s="188"/>
-      <c r="U8" s="189"/>
-      <c r="V8" s="190"/>
-      <c r="W8" s="183">
+      <c r="T8" s="156"/>
+      <c r="U8" s="157"/>
+      <c r="V8" s="158"/>
+      <c r="W8" s="151">
         <f>SUM(W6:Z6)</f>
         <v>22</v>
       </c>
-      <c r="X8" s="184"/>
-      <c r="Y8" s="185"/>
-      <c r="Z8" s="186"/>
-      <c r="AA8" s="192">
+      <c r="X8" s="152"/>
+      <c r="Y8" s="153"/>
+      <c r="Z8" s="154"/>
+      <c r="AA8" s="164">
         <f>SUM(AA6:AD6)</f>
         <v>14</v>
       </c>
-      <c r="AB8" s="193"/>
-      <c r="AC8" s="194"/>
-      <c r="AD8" s="195"/>
-      <c r="AE8" s="131">
+      <c r="AB8" s="165"/>
+      <c r="AC8" s="166"/>
+      <c r="AD8" s="167"/>
+      <c r="AE8" s="123">
         <f>SUM(AE6:AH6)</f>
         <v>12</v>
       </c>
-      <c r="AF8" s="132"/>
-      <c r="AG8" s="133"/>
-      <c r="AH8" s="134"/>
-      <c r="AI8" s="121">
+      <c r="AF8" s="124"/>
+      <c r="AG8" s="125"/>
+      <c r="AH8" s="126"/>
+      <c r="AI8" s="186">
         <f>SUM(AI6:AL6)</f>
         <v>7</v>
       </c>
-      <c r="AJ8" s="122"/>
-      <c r="AK8" s="123"/>
-      <c r="AL8" s="124"/>
-      <c r="AM8" s="135">
+      <c r="AJ8" s="187"/>
+      <c r="AK8" s="188"/>
+      <c r="AL8" s="189"/>
+      <c r="AM8" s="160">
         <f>SUM(AM6:AP6)</f>
         <v>2</v>
       </c>
-      <c r="AN8" s="136"/>
-      <c r="AO8" s="137"/>
-      <c r="AP8" s="138"/>
-      <c r="AQ8" s="135">
+      <c r="AN8" s="161"/>
+      <c r="AO8" s="162"/>
+      <c r="AP8" s="163"/>
+      <c r="AQ8" s="160">
         <f>SUM(AQ6:AT6)</f>
         <v>0</v>
       </c>
-      <c r="AR8" s="136"/>
-      <c r="AS8" s="137"/>
-      <c r="AT8" s="138"/>
-      <c r="AU8" s="131">
+      <c r="AR8" s="161"/>
+      <c r="AS8" s="162"/>
+      <c r="AT8" s="163"/>
+      <c r="AU8" s="123">
         <f>SUM(AU6:AX6)</f>
         <v>0</v>
       </c>
-      <c r="AV8" s="132"/>
-      <c r="AW8" s="133"/>
-      <c r="AX8" s="134"/>
-      <c r="AY8" s="121">
+      <c r="AV8" s="124"/>
+      <c r="AW8" s="125"/>
+      <c r="AX8" s="126"/>
+      <c r="AY8" s="186">
         <f>SUM(AY6:BB6)</f>
         <v>0</v>
       </c>
-      <c r="AZ8" s="122"/>
-      <c r="BA8" s="123"/>
-      <c r="BB8" s="124"/>
-      <c r="BC8" s="135">
+      <c r="AZ8" s="187"/>
+      <c r="BA8" s="188"/>
+      <c r="BB8" s="189"/>
+      <c r="BC8" s="160">
         <f>SUM(BC6:BF6)</f>
         <v>0</v>
       </c>
-      <c r="BD8" s="136"/>
-      <c r="BE8" s="137"/>
-      <c r="BF8" s="138"/>
-      <c r="BG8" s="135">
+      <c r="BD8" s="161"/>
+      <c r="BE8" s="162"/>
+      <c r="BF8" s="163"/>
+      <c r="BG8" s="160">
         <f>SUM(BG6:BJ6)</f>
         <v>0</v>
       </c>
-      <c r="BH8" s="136"/>
-      <c r="BI8" s="137"/>
-      <c r="BJ8" s="138"/>
-      <c r="BK8" s="131">
+      <c r="BH8" s="161"/>
+      <c r="BI8" s="162"/>
+      <c r="BJ8" s="163"/>
+      <c r="BK8" s="123">
         <f>SUM(BK6:BN6)</f>
         <v>0</v>
       </c>
-      <c r="BL8" s="132"/>
-      <c r="BM8" s="133"/>
-      <c r="BN8" s="134"/>
+      <c r="BL8" s="124"/>
+      <c r="BM8" s="125"/>
+      <c r="BN8" s="126"/>
     </row>
     <row r="9" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="125" t="s">
+      <c r="D9" s="190" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="143">
+      <c r="E9" s="148"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="195">
         <f>SUM(G8:V8)</f>
         <v>46</v>
       </c>
-      <c r="H9" s="143"/>
-      <c r="I9" s="144"/>
-      <c r="J9" s="144"/>
-      <c r="K9" s="144"/>
-      <c r="L9" s="144"/>
-      <c r="M9" s="144"/>
-      <c r="N9" s="144"/>
-      <c r="O9" s="144"/>
-      <c r="P9" s="144"/>
-      <c r="Q9" s="144"/>
-      <c r="R9" s="144"/>
-      <c r="S9" s="144"/>
-      <c r="T9" s="144"/>
-      <c r="U9" s="144"/>
-      <c r="V9" s="144"/>
-      <c r="W9" s="160">
+      <c r="H9" s="195"/>
+      <c r="I9" s="196"/>
+      <c r="J9" s="196"/>
+      <c r="K9" s="196"/>
+      <c r="L9" s="196"/>
+      <c r="M9" s="196"/>
+      <c r="N9" s="196"/>
+      <c r="O9" s="196"/>
+      <c r="P9" s="196"/>
+      <c r="Q9" s="196"/>
+      <c r="R9" s="196"/>
+      <c r="S9" s="196"/>
+      <c r="T9" s="196"/>
+      <c r="U9" s="196"/>
+      <c r="V9" s="196"/>
+      <c r="W9" s="135">
         <f>SUM(W8:AL8)</f>
         <v>55</v>
       </c>
-      <c r="X9" s="161"/>
-      <c r="Y9" s="161"/>
-      <c r="Z9" s="161"/>
-      <c r="AA9" s="161"/>
-      <c r="AB9" s="161"/>
-      <c r="AC9" s="161"/>
-      <c r="AD9" s="161"/>
-      <c r="AE9" s="161"/>
-      <c r="AF9" s="161"/>
-      <c r="AG9" s="161"/>
-      <c r="AH9" s="161"/>
-      <c r="AI9" s="161"/>
-      <c r="AJ9" s="161"/>
-      <c r="AK9" s="161"/>
-      <c r="AL9" s="162"/>
-      <c r="AM9" s="160">
+      <c r="X9" s="136"/>
+      <c r="Y9" s="136"/>
+      <c r="Z9" s="136"/>
+      <c r="AA9" s="136"/>
+      <c r="AB9" s="136"/>
+      <c r="AC9" s="136"/>
+      <c r="AD9" s="136"/>
+      <c r="AE9" s="136"/>
+      <c r="AF9" s="136"/>
+      <c r="AG9" s="136"/>
+      <c r="AH9" s="136"/>
+      <c r="AI9" s="136"/>
+      <c r="AJ9" s="136"/>
+      <c r="AK9" s="136"/>
+      <c r="AL9" s="175"/>
+      <c r="AM9" s="135">
         <f>SUM(AM8:BB8)</f>
         <v>2</v>
       </c>
-      <c r="AN9" s="161"/>
-      <c r="AO9" s="161"/>
-      <c r="AP9" s="161"/>
-      <c r="AQ9" s="161"/>
-      <c r="AR9" s="161"/>
-      <c r="AS9" s="161"/>
-      <c r="AT9" s="161"/>
-      <c r="AU9" s="161"/>
-      <c r="AV9" s="161"/>
-      <c r="AW9" s="161"/>
-      <c r="AX9" s="161"/>
-      <c r="AY9" s="161"/>
-      <c r="AZ9" s="161"/>
-      <c r="BA9" s="161"/>
-      <c r="BB9" s="161"/>
-      <c r="BC9" s="161"/>
-      <c r="BD9" s="161"/>
-      <c r="BE9" s="161"/>
-      <c r="BF9" s="161"/>
-      <c r="BG9" s="161"/>
-      <c r="BH9" s="161"/>
-      <c r="BI9" s="161"/>
-      <c r="BJ9" s="161"/>
+      <c r="AN9" s="136"/>
+      <c r="AO9" s="136"/>
+      <c r="AP9" s="136"/>
+      <c r="AQ9" s="136"/>
+      <c r="AR9" s="136"/>
+      <c r="AS9" s="136"/>
+      <c r="AT9" s="136"/>
+      <c r="AU9" s="136"/>
+      <c r="AV9" s="136"/>
+      <c r="AW9" s="136"/>
+      <c r="AX9" s="136"/>
+      <c r="AY9" s="136"/>
+      <c r="AZ9" s="136"/>
+      <c r="BA9" s="136"/>
+      <c r="BB9" s="136"/>
+      <c r="BC9" s="136"/>
+      <c r="BD9" s="136"/>
+      <c r="BE9" s="136"/>
+      <c r="BF9" s="136"/>
+      <c r="BG9" s="136"/>
+      <c r="BH9" s="136"/>
+      <c r="BI9" s="136"/>
+      <c r="BJ9" s="136"/>
       <c r="BK9" s="117"/>
       <c r="BL9" s="117"/>
       <c r="BM9" s="117"/>
       <c r="BN9" s="117"/>
     </row>
     <row r="10" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="125" t="s">
+      <c r="D10" s="190" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="126"/>
-      <c r="F10" s="126"/>
-      <c r="G10" s="171">
+      <c r="E10" s="148"/>
+      <c r="F10" s="148"/>
+      <c r="G10" s="137">
         <f>SUM(G8:BJ8)</f>
         <v>103</v>
       </c>
-      <c r="H10" s="172"/>
-      <c r="I10" s="172"/>
-      <c r="J10" s="172"/>
-      <c r="K10" s="172"/>
-      <c r="L10" s="172"/>
-      <c r="M10" s="172"/>
-      <c r="N10" s="172"/>
-      <c r="O10" s="172"/>
-      <c r="P10" s="172"/>
-      <c r="Q10" s="172"/>
-      <c r="R10" s="172"/>
-      <c r="S10" s="172"/>
-      <c r="T10" s="172"/>
-      <c r="U10" s="172"/>
-      <c r="V10" s="172"/>
-      <c r="W10" s="172"/>
-      <c r="X10" s="172"/>
-      <c r="Y10" s="172"/>
-      <c r="Z10" s="172"/>
-      <c r="AA10" s="172"/>
-      <c r="AB10" s="172"/>
-      <c r="AC10" s="172"/>
-      <c r="AD10" s="172"/>
-      <c r="AE10" s="172"/>
-      <c r="AF10" s="172"/>
-      <c r="AG10" s="172"/>
-      <c r="AH10" s="172"/>
-      <c r="AI10" s="172"/>
-      <c r="AJ10" s="172"/>
-      <c r="AK10" s="172"/>
-      <c r="AL10" s="172"/>
-      <c r="AM10" s="172"/>
-      <c r="AN10" s="172"/>
-      <c r="AO10" s="172"/>
-      <c r="AP10" s="172"/>
-      <c r="AQ10" s="172"/>
-      <c r="AR10" s="172"/>
-      <c r="AS10" s="172"/>
-      <c r="AT10" s="172"/>
-      <c r="AU10" s="172"/>
-      <c r="AV10" s="172"/>
-      <c r="AW10" s="172"/>
-      <c r="AX10" s="172"/>
-      <c r="AY10" s="172"/>
-      <c r="AZ10" s="172"/>
-      <c r="BA10" s="172"/>
-      <c r="BB10" s="172"/>
-      <c r="BC10" s="172"/>
-      <c r="BD10" s="172"/>
-      <c r="BE10" s="172"/>
-      <c r="BF10" s="172"/>
-      <c r="BG10" s="172"/>
-      <c r="BH10" s="172"/>
-      <c r="BI10" s="172"/>
-      <c r="BJ10" s="172"/>
+      <c r="H10" s="138"/>
+      <c r="I10" s="138"/>
+      <c r="J10" s="138"/>
+      <c r="K10" s="138"/>
+      <c r="L10" s="138"/>
+      <c r="M10" s="138"/>
+      <c r="N10" s="138"/>
+      <c r="O10" s="138"/>
+      <c r="P10" s="138"/>
+      <c r="Q10" s="138"/>
+      <c r="R10" s="138"/>
+      <c r="S10" s="138"/>
+      <c r="T10" s="138"/>
+      <c r="U10" s="138"/>
+      <c r="V10" s="138"/>
+      <c r="W10" s="138"/>
+      <c r="X10" s="138"/>
+      <c r="Y10" s="138"/>
+      <c r="Z10" s="138"/>
+      <c r="AA10" s="138"/>
+      <c r="AB10" s="138"/>
+      <c r="AC10" s="138"/>
+      <c r="AD10" s="138"/>
+      <c r="AE10" s="138"/>
+      <c r="AF10" s="138"/>
+      <c r="AG10" s="138"/>
+      <c r="AH10" s="138"/>
+      <c r="AI10" s="138"/>
+      <c r="AJ10" s="138"/>
+      <c r="AK10" s="138"/>
+      <c r="AL10" s="138"/>
+      <c r="AM10" s="138"/>
+      <c r="AN10" s="138"/>
+      <c r="AO10" s="138"/>
+      <c r="AP10" s="138"/>
+      <c r="AQ10" s="138"/>
+      <c r="AR10" s="138"/>
+      <c r="AS10" s="138"/>
+      <c r="AT10" s="138"/>
+      <c r="AU10" s="138"/>
+      <c r="AV10" s="138"/>
+      <c r="AW10" s="138"/>
+      <c r="AX10" s="138"/>
+      <c r="AY10" s="138"/>
+      <c r="AZ10" s="138"/>
+      <c r="BA10" s="138"/>
+      <c r="BB10" s="138"/>
+      <c r="BC10" s="138"/>
+      <c r="BD10" s="138"/>
+      <c r="BE10" s="138"/>
+      <c r="BF10" s="138"/>
+      <c r="BG10" s="138"/>
+      <c r="BH10" s="138"/>
+      <c r="BI10" s="138"/>
+      <c r="BJ10" s="138"/>
       <c r="BK10" s="118"/>
       <c r="BL10" s="118"/>
       <c r="BM10" s="118"/>
@@ -5942,6 +5942,7 @@
       <c r="BJ13" s="31"/>
     </row>
     <row r="14" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="97"/>
       <c r="B14" t="s">
         <v>25</v>
       </c>
@@ -6017,6 +6018,7 @@
       <c r="BJ14" s="31"/>
     </row>
     <row r="15" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="97"/>
       <c r="B15" t="s">
         <v>28</v>
       </c>
@@ -6095,6 +6097,7 @@
       <c r="BJ15" s="31"/>
     </row>
     <row r="16" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="97"/>
       <c r="B16" t="s">
         <v>31</v>
       </c>
@@ -6185,7 +6188,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="97"/>
       <c r="B17" t="s">
         <v>34</v>
       </c>
@@ -6269,7 +6273,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="97"/>
       <c r="B18" t="s">
         <v>43</v>
       </c>
@@ -6351,7 +6356,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="97"/>
       <c r="B19" t="s">
         <v>37</v>
       </c>
@@ -6437,7 +6443,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="97"/>
       <c r="B20" t="s">
         <v>40</v>
       </c>
@@ -6537,7 +6544,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="97"/>
       <c r="B21" s="2" t="s">
         <v>792</v>
       </c>
@@ -6582,7 +6590,8 @@
       <c r="BI21" s="31"/>
       <c r="BJ21" s="31"/>
     </row>
-    <row r="22" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A22" s="97"/>
       <c r="B22" t="s">
         <v>46</v>
       </c>
@@ -6682,7 +6691,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A23" s="97"/>
       <c r="B23" t="s">
         <v>49</v>
       </c>
@@ -6782,7 +6792,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="97"/>
       <c r="B24" t="s">
         <v>55</v>
       </c>
@@ -6858,7 +6869,8 @@
       <c r="BJ24" s="31"/>
       <c r="BK24" s="48"/>
     </row>
-    <row r="25" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="97"/>
       <c r="B25" t="s">
         <v>58</v>
       </c>
@@ -6956,7 +6968,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="97"/>
       <c r="B26" t="s">
         <v>52</v>
       </c>
@@ -7037,7 +7050,8 @@
       <c r="BL26" s="37"/>
       <c r="BM26" s="37"/>
     </row>
-    <row r="27" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="97"/>
       <c r="B27" t="s">
         <v>61</v>
       </c>
@@ -7110,7 +7124,8 @@
       <c r="BJ27" s="31"/>
       <c r="BK27" s="48"/>
     </row>
-    <row r="28" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="97"/>
       <c r="B28" t="s">
         <v>64</v>
       </c>
@@ -7208,7 +7223,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="97"/>
       <c r="B29" t="s">
         <v>67</v>
       </c>
@@ -7277,7 +7293,8 @@
       <c r="BI29" s="31"/>
       <c r="BJ29" s="31"/>
     </row>
-    <row r="30" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="97"/>
       <c r="B30" t="s">
         <v>70</v>
       </c>
@@ -7358,7 +7375,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="97"/>
       <c r="B31" t="s">
         <v>73</v>
       </c>
@@ -7439,7 +7457,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="97"/>
       <c r="B32" t="s">
         <v>79</v>
       </c>
@@ -7544,7 +7563,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="97"/>
       <c r="B33" t="s">
         <v>76</v>
       </c>
@@ -7603,7 +7623,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="97"/>
       <c r="B34" t="s">
         <v>82</v>
       </c>
@@ -7662,7 +7683,8 @@
       <c r="BI34" s="31"/>
       <c r="BJ34" s="31"/>
     </row>
-    <row r="35" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A35" s="97"/>
       <c r="B35" s="2" t="s">
         <v>793</v>
       </c>
@@ -7716,7 +7738,8 @@
       <c r="BI35" s="31"/>
       <c r="BJ35" s="31"/>
     </row>
-    <row r="36" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A36" s="97"/>
       <c r="B36" t="s">
         <v>85</v>
       </c>
@@ -7784,7 +7807,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="37" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A37" s="97"/>
       <c r="B37" t="s">
         <v>88</v>
       </c>
@@ -7852,7 +7876,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="38" spans="2:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="97"/>
       <c r="B38" t="s">
         <v>91</v>
       </c>
@@ -7958,7 +7983,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A39" s="97"/>
       <c r="B39" t="s">
         <v>94</v>
       </c>
@@ -8071,7 +8097,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A40" s="97"/>
       <c r="B40" t="s">
         <v>100</v>
       </c>
@@ -8163,7 +8190,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="41" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A41" s="97"/>
       <c r="B41" t="s">
         <v>103</v>
       </c>
@@ -8255,7 +8283,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="42" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A42" s="97"/>
       <c r="B42" t="s">
         <v>97</v>
       </c>
@@ -8342,7 +8371,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A43" s="97"/>
       <c r="B43" t="s">
         <v>106</v>
       </c>
@@ -8422,7 +8452,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A44" s="97"/>
       <c r="B44" t="s">
         <v>109</v>
       </c>
@@ -8509,7 +8540,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="45" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A45" s="97"/>
       <c r="B45" t="s">
         <v>112</v>
       </c>
@@ -8582,7 +8614,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="46" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A46" s="97"/>
       <c r="B46" t="s">
         <v>115</v>
       </c>
@@ -8650,7 +8683,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="47" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A47" s="97"/>
       <c r="B47" t="s">
         <v>118</v>
       </c>
@@ -8711,7 +8745,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="48" spans="2:66" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A48" s="97"/>
       <c r="B48" t="s">
         <v>121</v>
       </c>
@@ -8773,6 +8808,7 @@
       </c>
     </row>
     <row r="49" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A49" s="97"/>
       <c r="B49" s="2" t="s">
         <v>795</v>
       </c>
@@ -8818,6 +8854,7 @@
       <c r="BJ49" s="31"/>
     </row>
     <row r="50" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A50" s="97"/>
       <c r="B50" t="s">
         <v>133</v>
       </c>
@@ -8881,6 +8918,7 @@
       <c r="BJ50" s="31"/>
     </row>
     <row r="51" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A51" s="97"/>
       <c r="B51" t="s">
         <v>136</v>
       </c>
@@ -8990,6 +9028,7 @@
       <c r="BN51" s="37"/>
     </row>
     <row r="52" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A52" s="97"/>
       <c r="B52" t="s">
         <v>139</v>
       </c>
@@ -9095,6 +9134,7 @@
       <c r="BJ52" s="31"/>
     </row>
     <row r="53" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A53" s="97"/>
       <c r="B53" t="s">
         <v>142</v>
       </c>
@@ -9200,6 +9240,7 @@
       <c r="BJ53" s="31"/>
     </row>
     <row r="54" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A54" s="97"/>
       <c r="B54" t="s">
         <v>124</v>
       </c>
@@ -9285,6 +9326,7 @@
       <c r="BM54" s="37"/>
     </row>
     <row r="55" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A55" s="97"/>
       <c r="B55" t="s">
         <v>127</v>
       </c>
@@ -9377,6 +9419,7 @@
       <c r="BM55" s="37"/>
     </row>
     <row r="56" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A56" s="97"/>
       <c r="B56" t="s">
         <v>130</v>
       </c>
@@ -9469,6 +9512,7 @@
       <c r="BM56" s="37"/>
     </row>
     <row r="57" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A57" s="97"/>
       <c r="B57" t="s">
         <v>145</v>
       </c>
@@ -12970,7 +13014,7 @@
       <c r="BN107" s="33"/>
     </row>
     <row r="108" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A108" s="120" t="s">
+      <c r="A108" s="185" t="s">
         <v>774</v>
       </c>
       <c r="B108" t="s">
@@ -12980,7 +13024,7 @@
         <v>6</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" ref="D108:D118" si="13">COUNTIF(G108:AAN108,"✅")+COUNTIF(G108:AAN108,"✔️")</f>
+        <f t="shared" ref="D108:D144" si="13">COUNTIF(G108:AAN108,"✅")+COUNTIF(G108:AAN108,"✔️")</f>
         <v>9</v>
       </c>
       <c r="E108" t="s">
@@ -13040,7 +13084,7 @@
       <c r="BJ108" s="31"/>
     </row>
     <row r="109" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A109" s="120"/>
+      <c r="A109" s="185"/>
       <c r="B109" t="s">
         <v>284</v>
       </c>
@@ -13108,7 +13152,7 @@
       <c r="BJ109" s="31"/>
     </row>
     <row r="110" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A110" s="120"/>
+      <c r="A110" s="185"/>
       <c r="B110" t="s">
         <v>287</v>
       </c>
@@ -13176,7 +13220,7 @@
       <c r="BJ110" s="31"/>
     </row>
     <row r="111" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A111" s="120"/>
+      <c r="A111" s="185"/>
       <c r="B111" t="s">
         <v>290</v>
       </c>
@@ -13243,7 +13287,7 @@
       <c r="BJ111" s="31"/>
     </row>
     <row r="112" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A112" s="120"/>
+      <c r="A112" s="185"/>
       <c r="B112" t="s">
         <v>293</v>
       </c>
@@ -13310,7 +13354,7 @@
       <c r="BJ112" s="31"/>
     </row>
     <row r="113" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A113" s="120"/>
+      <c r="A113" s="185"/>
       <c r="B113" t="s">
         <v>296</v>
       </c>
@@ -13377,7 +13421,7 @@
       <c r="BJ113" s="31"/>
     </row>
     <row r="114" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A114" s="120"/>
+      <c r="A114" s="185"/>
       <c r="B114" t="s">
         <v>299</v>
       </c>
@@ -13444,7 +13488,7 @@
       <c r="BJ114" s="31"/>
     </row>
     <row r="115" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A115" s="120"/>
+      <c r="A115" s="185"/>
       <c r="B115" t="s">
         <v>302</v>
       </c>
@@ -13556,7 +13600,9 @@
       <c r="BN116" s="33"/>
     </row>
     <row r="117" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A117" s="119"/>
+      <c r="A117" s="203" t="s">
+        <v>280</v>
+      </c>
       <c r="B117" t="s">
         <v>852</v>
       </c>
@@ -13608,7 +13654,7 @@
       <c r="BJ117" s="31"/>
     </row>
     <row r="118" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A118" s="119"/>
+      <c r="A118" s="203"/>
       <c r="B118" t="s">
         <v>854</v>
       </c>
@@ -13660,12 +13706,16 @@
       <c r="BJ118" s="31"/>
     </row>
     <row r="119" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A119" s="119"/>
+      <c r="A119" s="203"/>
       <c r="B119" t="s">
         <v>856</v>
       </c>
       <c r="C119" s="11">
         <v>4</v>
+      </c>
+      <c r="D119" s="1">
+        <f t="shared" si="13"/>
+        <v>8</v>
       </c>
       <c r="E119" t="s">
         <v>857</v>
@@ -13710,7 +13760,11 @@
       <c r="BJ119" s="31"/>
     </row>
     <row r="120" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A120" s="119"/>
+      <c r="A120" s="203"/>
+      <c r="D120" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM120" s="51"/>
       <c r="AP120" s="52"/>
       <c r="AQ120" s="51"/>
@@ -13729,7 +13783,11 @@
       <c r="BJ120" s="31"/>
     </row>
     <row r="121" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A121" s="119"/>
+      <c r="A121" s="203"/>
+      <c r="D121" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM121" s="51"/>
       <c r="AP121" s="52"/>
       <c r="AQ121" s="51"/>
@@ -13748,7 +13806,11 @@
       <c r="BJ121" s="31"/>
     </row>
     <row r="122" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A122" s="119"/>
+      <c r="A122" s="203"/>
+      <c r="D122" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM122" s="51"/>
       <c r="AP122" s="52"/>
       <c r="AQ122" s="51"/>
@@ -13767,7 +13829,11 @@
       <c r="BJ122" s="31"/>
     </row>
     <row r="123" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A123" s="119"/>
+      <c r="A123" s="203"/>
+      <c r="D123" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM123" s="51"/>
       <c r="AP123" s="52"/>
       <c r="AQ123" s="51"/>
@@ -13785,20 +13851,11 @@
       <c r="BI123" s="31"/>
       <c r="BJ123" s="31"/>
     </row>
-    <row r="124" spans="1:66" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="119"/>
-      <c r="B124" t="s">
-        <v>775</v>
-      </c>
+    <row r="124" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A124" s="203"/>
       <c r="D124" s="1">
-        <f>COUNTIF(G124:AAN124,"✅")+COUNTIF(G124:AAN124,"✔️")</f>
-        <v>9</v>
-      </c>
-      <c r="E124" t="s">
-        <v>306</v>
-      </c>
-      <c r="F124" t="s">
-        <v>307</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="AM124" s="51"/>
       <c r="AP124" s="52"/>
@@ -13808,48 +13865,20 @@
       <c r="AV124"/>
       <c r="AW124"/>
       <c r="AX124" s="52"/>
-      <c r="BC124" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD124" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE124" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG124" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH124" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI124" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK124" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL124" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM124" s="30" t="s">
-        <v>24</v>
-      </c>
+      <c r="BC124" s="62"/>
+      <c r="BD124" s="31"/>
+      <c r="BE124" s="31"/>
+      <c r="BF124" s="31"/>
+      <c r="BG124" s="62"/>
+      <c r="BH124" s="31"/>
+      <c r="BI124" s="31"/>
+      <c r="BJ124" s="31"/>
     </row>
     <row r="125" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A125" s="119"/>
-      <c r="B125" t="s">
-        <v>776</v>
-      </c>
+      <c r="A125" s="203"/>
       <c r="D125" s="1">
-        <f t="shared" ref="D125:D140" si="14">COUNTIF(G125:AAN125,"✅")+COUNTIF(G125:AAN125,"✔️")</f>
-        <v>9</v>
-      </c>
-      <c r="E125" t="s">
-        <v>309</v>
-      </c>
-      <c r="F125" t="s">
-        <v>310</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="AM125" s="51"/>
       <c r="AP125" s="52"/>
@@ -13859,48 +13888,20 @@
       <c r="AV125"/>
       <c r="AW125"/>
       <c r="AX125" s="52"/>
-      <c r="BC125" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD125" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE125" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG125" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH125" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI125" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK125" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL125" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM125" s="30" t="s">
-        <v>24</v>
-      </c>
+      <c r="BC125" s="62"/>
+      <c r="BD125" s="31"/>
+      <c r="BE125" s="31"/>
+      <c r="BF125" s="31"/>
+      <c r="BG125" s="62"/>
+      <c r="BH125" s="31"/>
+      <c r="BI125" s="31"/>
+      <c r="BJ125" s="31"/>
     </row>
     <row r="126" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A126" s="119"/>
-      <c r="B126" t="s">
-        <v>777</v>
-      </c>
+      <c r="A126" s="203"/>
       <c r="D126" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="E126" t="s">
-        <v>312</v>
-      </c>
-      <c r="F126" t="s">
-        <v>313</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="AM126" s="51"/>
       <c r="AP126" s="52"/>
@@ -13910,48 +13911,20 @@
       <c r="AV126"/>
       <c r="AW126"/>
       <c r="AX126" s="52"/>
-      <c r="BC126" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD126" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE126" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG126" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH126" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI126" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK126" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL126" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM126" s="30" t="s">
-        <v>24</v>
-      </c>
+      <c r="BC126" s="62"/>
+      <c r="BD126" s="31"/>
+      <c r="BE126" s="31"/>
+      <c r="BF126" s="31"/>
+      <c r="BG126" s="62"/>
+      <c r="BH126" s="31"/>
+      <c r="BI126" s="31"/>
+      <c r="BJ126" s="31"/>
     </row>
     <row r="127" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A127" s="119"/>
-      <c r="B127" t="s">
-        <v>778</v>
-      </c>
+      <c r="A127" s="203"/>
       <c r="D127" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="E127" t="s">
-        <v>315</v>
-      </c>
-      <c r="F127" t="s">
-        <v>316</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="AM127" s="51"/>
       <c r="AP127" s="52"/>
@@ -13961,48 +13934,20 @@
       <c r="AV127"/>
       <c r="AW127"/>
       <c r="AX127" s="52"/>
-      <c r="BC127" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD127" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE127" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG127" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH127" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI127" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK127" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL127" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM127" s="30" t="s">
-        <v>24</v>
-      </c>
+      <c r="BC127" s="62"/>
+      <c r="BD127" s="31"/>
+      <c r="BE127" s="31"/>
+      <c r="BF127" s="31"/>
+      <c r="BG127" s="62"/>
+      <c r="BH127" s="31"/>
+      <c r="BI127" s="31"/>
+      <c r="BJ127" s="31"/>
     </row>
     <row r="128" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A128" s="119"/>
-      <c r="B128" t="s">
-        <v>779</v>
-      </c>
+      <c r="A128" s="203"/>
       <c r="D128" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="E128" t="s">
-        <v>318</v>
-      </c>
-      <c r="F128" t="s">
-        <v>319</v>
+        <f t="shared" si="13"/>
+        <v>0</v>
       </c>
       <c r="AM128" s="51"/>
       <c r="AP128" s="52"/>
@@ -14012,77 +13957,21 @@
       <c r="AV128"/>
       <c r="AW128"/>
       <c r="AX128" s="52"/>
-      <c r="BC128" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD128" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE128" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG128" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH128" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI128" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK128" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL128" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM128" s="30" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="129" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A129" s="119"/>
-      <c r="B129" t="s">
-        <v>780</v>
-      </c>
+      <c r="BC128" s="62"/>
+      <c r="BD128" s="31"/>
+      <c r="BE128" s="31"/>
+      <c r="BF128" s="31"/>
+      <c r="BG128" s="62"/>
+      <c r="BH128" s="31"/>
+      <c r="BI128" s="31"/>
+      <c r="BJ128" s="31"/>
+    </row>
+    <row r="129" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A129" s="203"/>
       <c r="D129" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="E129" t="s">
-        <v>321</v>
-      </c>
-      <c r="F129" t="s">
-        <v>322</v>
-      </c>
-      <c r="G129" s="51"/>
-      <c r="H129"/>
-      <c r="I129"/>
-      <c r="J129"/>
-      <c r="K129" s="51"/>
-      <c r="L129"/>
-      <c r="M129"/>
-      <c r="N129"/>
-      <c r="O129" s="51"/>
-      <c r="P129"/>
-      <c r="Q129"/>
-      <c r="R129"/>
-      <c r="S129" s="51"/>
-      <c r="T129"/>
-      <c r="U129"/>
-      <c r="V129"/>
-      <c r="W129" s="51"/>
-      <c r="X129"/>
-      <c r="Y129"/>
-      <c r="Z129"/>
-      <c r="AA129" s="51"/>
-      <c r="AB129"/>
-      <c r="AC129"/>
-      <c r="AD129"/>
-      <c r="AE129" s="51"/>
-      <c r="AF129"/>
-      <c r="AG129"/>
-      <c r="AH129"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM129" s="51"/>
       <c r="AP129" s="52"/>
       <c r="AQ129" s="51"/>
@@ -14091,78 +13980,21 @@
       <c r="AV129"/>
       <c r="AW129"/>
       <c r="AX129" s="52"/>
-      <c r="BC129" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD129" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE129" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG129" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH129" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI129" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK129" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL129" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM129" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BN129"/>
-    </row>
-    <row r="130" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A130" s="119"/>
-      <c r="B130" t="s">
-        <v>781</v>
-      </c>
+      <c r="BC129" s="62"/>
+      <c r="BD129" s="31"/>
+      <c r="BE129" s="31"/>
+      <c r="BF129" s="31"/>
+      <c r="BG129" s="62"/>
+      <c r="BH129" s="31"/>
+      <c r="BI129" s="31"/>
+      <c r="BJ129" s="31"/>
+    </row>
+    <row r="130" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A130" s="203"/>
       <c r="D130" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="E130" t="s">
-        <v>324</v>
-      </c>
-      <c r="F130" t="s">
-        <v>325</v>
-      </c>
-      <c r="G130" s="51"/>
-      <c r="H130"/>
-      <c r="I130"/>
-      <c r="J130"/>
-      <c r="K130" s="51"/>
-      <c r="L130"/>
-      <c r="M130"/>
-      <c r="N130"/>
-      <c r="O130" s="51"/>
-      <c r="P130"/>
-      <c r="Q130"/>
-      <c r="R130"/>
-      <c r="S130" s="51"/>
-      <c r="T130"/>
-      <c r="U130"/>
-      <c r="V130"/>
-      <c r="W130" s="51"/>
-      <c r="X130"/>
-      <c r="Y130"/>
-      <c r="Z130"/>
-      <c r="AA130" s="51"/>
-      <c r="AB130"/>
-      <c r="AC130"/>
-      <c r="AD130"/>
-      <c r="AE130" s="51"/>
-      <c r="AF130"/>
-      <c r="AG130"/>
-      <c r="AH130"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM130" s="51"/>
       <c r="AP130" s="52"/>
       <c r="AQ130" s="51"/>
@@ -14171,78 +14003,21 @@
       <c r="AV130"/>
       <c r="AW130"/>
       <c r="AX130" s="52"/>
-      <c r="BC130" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD130" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE130" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG130" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH130" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI130" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK130" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL130" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM130" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BN130"/>
-    </row>
-    <row r="131" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A131" s="119"/>
-      <c r="B131" t="s">
-        <v>782</v>
-      </c>
+      <c r="BC130" s="62"/>
+      <c r="BD130" s="31"/>
+      <c r="BE130" s="31"/>
+      <c r="BF130" s="31"/>
+      <c r="BG130" s="62"/>
+      <c r="BH130" s="31"/>
+      <c r="BI130" s="31"/>
+      <c r="BJ130" s="31"/>
+    </row>
+    <row r="131" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A131" s="203"/>
       <c r="D131" s="1">
-        <f t="shared" si="14"/>
-        <v>9</v>
-      </c>
-      <c r="E131" t="s">
-        <v>327</v>
-      </c>
-      <c r="F131" t="s">
-        <v>328</v>
-      </c>
-      <c r="G131" s="51"/>
-      <c r="H131"/>
-      <c r="I131"/>
-      <c r="J131"/>
-      <c r="K131" s="51"/>
-      <c r="L131"/>
-      <c r="M131"/>
-      <c r="N131"/>
-      <c r="O131" s="51"/>
-      <c r="P131"/>
-      <c r="Q131"/>
-      <c r="R131"/>
-      <c r="S131" s="51"/>
-      <c r="T131"/>
-      <c r="U131"/>
-      <c r="V131"/>
-      <c r="W131" s="51"/>
-      <c r="X131"/>
-      <c r="Y131"/>
-      <c r="Z131"/>
-      <c r="AA131" s="51"/>
-      <c r="AB131"/>
-      <c r="AC131"/>
-      <c r="AD131"/>
-      <c r="AE131" s="51"/>
-      <c r="AF131"/>
-      <c r="AG131"/>
-      <c r="AH131"/>
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
       <c r="AM131" s="51"/>
       <c r="AP131" s="52"/>
       <c r="AQ131" s="51"/>
@@ -14251,487 +14026,1278 @@
       <c r="AV131"/>
       <c r="AW131"/>
       <c r="AX131" s="52"/>
-      <c r="BC131" s="30" t="s">
-        <v>23</v>
-      </c>
-      <c r="BD131" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BE131" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BG131" s="80" t="s">
-        <v>24</v>
-      </c>
-      <c r="BH131" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BI131" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BK131" s="76" t="s">
-        <v>24</v>
-      </c>
-      <c r="BL131" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BM131" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="BN131"/>
-    </row>
-    <row r="132" spans="1:66" s="8" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="119"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="10"/>
-      <c r="G132" s="50"/>
-      <c r="H132" s="38"/>
-      <c r="I132" s="38"/>
-      <c r="J132" s="38"/>
-      <c r="K132" s="50"/>
-      <c r="L132" s="38"/>
-      <c r="M132" s="38"/>
-      <c r="N132" s="38"/>
-      <c r="O132" s="66"/>
-      <c r="P132" s="33"/>
-      <c r="Q132" s="33"/>
-      <c r="R132" s="33"/>
-      <c r="S132" s="66"/>
-      <c r="T132" s="33"/>
-      <c r="U132" s="33"/>
-      <c r="V132" s="33"/>
-      <c r="W132" s="66"/>
-      <c r="X132" s="33"/>
-      <c r="Y132" s="33"/>
-      <c r="Z132" s="33"/>
-      <c r="AA132" s="66"/>
-      <c r="AB132" s="33"/>
-      <c r="AC132" s="33"/>
-      <c r="AD132" s="33"/>
-      <c r="AE132" s="66"/>
-      <c r="AF132" s="33"/>
-      <c r="AG132" s="33"/>
-      <c r="AH132" s="33"/>
-      <c r="AI132" s="84"/>
-      <c r="AL132" s="83"/>
-      <c r="AU132" s="66"/>
-      <c r="AV132" s="33"/>
-      <c r="AW132" s="33"/>
-      <c r="AX132" s="33"/>
-      <c r="AY132" s="84"/>
-      <c r="BB132" s="83"/>
-      <c r="BK132" s="66"/>
-      <c r="BL132" s="33"/>
-      <c r="BM132" s="33"/>
-      <c r="BN132" s="33"/>
-    </row>
-    <row r="133" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A133" s="119"/>
-      <c r="B133" t="s">
-        <v>305</v>
-      </c>
+      <c r="BC131" s="62"/>
+      <c r="BD131" s="31"/>
+      <c r="BE131" s="31"/>
+      <c r="BF131" s="31"/>
+      <c r="BG131" s="62"/>
+      <c r="BH131" s="31"/>
+      <c r="BI131" s="31"/>
+      <c r="BJ131" s="31"/>
+    </row>
+    <row r="132" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A132" s="203"/>
+      <c r="D132" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM132" s="51"/>
+      <c r="AP132" s="52"/>
+      <c r="AQ132" s="51"/>
+      <c r="AT132" s="52"/>
+      <c r="AU132" s="51"/>
+      <c r="AV132"/>
+      <c r="AW132"/>
+      <c r="AX132" s="52"/>
+      <c r="BC132" s="62"/>
+      <c r="BD132" s="31"/>
+      <c r="BE132" s="31"/>
+      <c r="BF132" s="31"/>
+      <c r="BG132" s="62"/>
+      <c r="BH132" s="31"/>
+      <c r="BI132" s="31"/>
+      <c r="BJ132" s="31"/>
+    </row>
+    <row r="133" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A133" s="203"/>
       <c r="D133" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F133" t="s">
-        <v>329</v>
-      </c>
-      <c r="G133" s="51"/>
-      <c r="H133"/>
-      <c r="I133"/>
-      <c r="J133"/>
-      <c r="K133" s="51"/>
-      <c r="L133"/>
-      <c r="M133"/>
-      <c r="N133"/>
-      <c r="O133" s="51"/>
-      <c r="P133"/>
-      <c r="Q133"/>
-      <c r="R133"/>
-      <c r="S133" s="51"/>
-      <c r="T133"/>
-      <c r="U133"/>
-      <c r="V133"/>
-      <c r="W133" s="51"/>
-      <c r="X133"/>
-      <c r="Y133"/>
-      <c r="Z133"/>
-      <c r="AA133" s="51"/>
-      <c r="AB133"/>
-      <c r="AC133"/>
-      <c r="AD133"/>
-      <c r="AE133" s="51"/>
-      <c r="AF133"/>
-      <c r="AG133"/>
-      <c r="AH133"/>
+      <c r="AM133" s="51"/>
+      <c r="AP133" s="52"/>
+      <c r="AQ133" s="51"/>
+      <c r="AT133" s="52"/>
       <c r="AU133" s="51"/>
       <c r="AV133"/>
       <c r="AW133"/>
-      <c r="AX133"/>
-      <c r="BK133" s="51"/>
-      <c r="BL133"/>
-      <c r="BM133"/>
-      <c r="BN133"/>
-    </row>
-    <row r="134" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A134" s="119"/>
-      <c r="B134" t="s">
-        <v>308</v>
-      </c>
+      <c r="AX133" s="52"/>
+      <c r="BC133" s="62"/>
+      <c r="BD133" s="31"/>
+      <c r="BE133" s="31"/>
+      <c r="BF133" s="31"/>
+      <c r="BG133" s="62"/>
+      <c r="BH133" s="31"/>
+      <c r="BI133" s="31"/>
+      <c r="BJ133" s="31"/>
+    </row>
+    <row r="134" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A134" s="203"/>
       <c r="D134" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="E134" t="s">
-        <v>330</v>
-      </c>
-      <c r="F134" t="s">
-        <v>331</v>
-      </c>
-      <c r="G134" s="51"/>
-      <c r="H134"/>
-      <c r="I134"/>
-      <c r="J134"/>
-      <c r="K134" s="51"/>
-      <c r="L134"/>
-      <c r="M134"/>
-      <c r="N134"/>
-      <c r="O134" s="51"/>
-      <c r="P134"/>
-      <c r="Q134"/>
-      <c r="R134"/>
-      <c r="S134" s="51"/>
-      <c r="T134"/>
-      <c r="U134"/>
-      <c r="V134"/>
-      <c r="W134" s="51"/>
-      <c r="X134"/>
-      <c r="Y134"/>
-      <c r="Z134"/>
-      <c r="AA134" s="51"/>
-      <c r="AB134"/>
-      <c r="AC134"/>
-      <c r="AD134"/>
-      <c r="AE134" s="51"/>
-      <c r="AF134"/>
-      <c r="AG134"/>
-      <c r="AH134"/>
+      <c r="AM134" s="51"/>
+      <c r="AP134" s="52"/>
+      <c r="AQ134" s="51"/>
+      <c r="AT134" s="52"/>
       <c r="AU134" s="51"/>
       <c r="AV134"/>
       <c r="AW134"/>
-      <c r="AX134"/>
-      <c r="BK134" s="51"/>
-      <c r="BL134"/>
-      <c r="BM134"/>
-      <c r="BN134"/>
-    </row>
-    <row r="135" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A135" s="119"/>
-      <c r="B135" t="s">
-        <v>311</v>
-      </c>
+      <c r="AX134" s="52"/>
+      <c r="BC134" s="62"/>
+      <c r="BD134" s="31"/>
+      <c r="BE134" s="31"/>
+      <c r="BF134" s="31"/>
+      <c r="BG134" s="62"/>
+      <c r="BH134" s="31"/>
+      <c r="BI134" s="31"/>
+      <c r="BJ134" s="31"/>
+    </row>
+    <row r="135" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A135" s="203"/>
       <c r="D135" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F135" t="s">
-        <v>332</v>
-      </c>
-      <c r="G135" s="51"/>
-      <c r="H135"/>
-      <c r="I135"/>
-      <c r="J135"/>
-      <c r="K135" s="51"/>
-      <c r="L135"/>
-      <c r="M135"/>
-      <c r="N135"/>
-      <c r="O135" s="51"/>
-      <c r="P135"/>
-      <c r="Q135"/>
-      <c r="R135"/>
-      <c r="S135" s="51"/>
-      <c r="T135"/>
-      <c r="U135"/>
-      <c r="V135"/>
-      <c r="W135" s="51"/>
-      <c r="X135"/>
-      <c r="Y135"/>
-      <c r="Z135"/>
-      <c r="AA135" s="51"/>
-      <c r="AB135"/>
-      <c r="AC135"/>
-      <c r="AD135"/>
-      <c r="AE135" s="51"/>
-      <c r="AF135"/>
-      <c r="AG135"/>
-      <c r="AH135"/>
+      <c r="AM135" s="51"/>
+      <c r="AP135" s="52"/>
+      <c r="AQ135" s="51"/>
+      <c r="AT135" s="52"/>
       <c r="AU135" s="51"/>
       <c r="AV135"/>
       <c r="AW135"/>
-      <c r="AX135"/>
-      <c r="BK135" s="51"/>
-      <c r="BL135"/>
-      <c r="BM135"/>
-      <c r="BN135"/>
-    </row>
-    <row r="136" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A136" s="119"/>
-      <c r="B136" t="s">
-        <v>314</v>
-      </c>
+      <c r="AX135" s="52"/>
+      <c r="BC135" s="62"/>
+      <c r="BD135" s="31"/>
+      <c r="BE135" s="31"/>
+      <c r="BF135" s="31"/>
+      <c r="BG135" s="62"/>
+      <c r="BH135" s="31"/>
+      <c r="BI135" s="31"/>
+      <c r="BJ135" s="31"/>
+    </row>
+    <row r="136" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A136" s="203"/>
       <c r="D136" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F136" t="s">
-        <v>333</v>
-      </c>
-      <c r="G136" s="51"/>
-      <c r="H136"/>
-      <c r="I136"/>
-      <c r="J136"/>
-      <c r="K136" s="51"/>
-      <c r="L136"/>
-      <c r="M136"/>
-      <c r="N136"/>
-      <c r="O136" s="51"/>
-      <c r="P136"/>
-      <c r="Q136"/>
-      <c r="R136"/>
-      <c r="S136" s="51"/>
-      <c r="T136"/>
-      <c r="U136"/>
-      <c r="V136"/>
-      <c r="W136" s="51"/>
-      <c r="X136"/>
-      <c r="Y136"/>
-      <c r="Z136"/>
-      <c r="AA136" s="51"/>
-      <c r="AB136"/>
-      <c r="AC136"/>
-      <c r="AD136"/>
-      <c r="AE136" s="51"/>
-      <c r="AF136"/>
-      <c r="AG136"/>
-      <c r="AH136"/>
+      <c r="AM136" s="51"/>
+      <c r="AP136" s="52"/>
+      <c r="AQ136" s="51"/>
+      <c r="AT136" s="52"/>
       <c r="AU136" s="51"/>
       <c r="AV136"/>
       <c r="AW136"/>
-      <c r="AX136"/>
-      <c r="BK136" s="51"/>
-      <c r="BL136"/>
-      <c r="BM136"/>
-      <c r="BN136"/>
-    </row>
-    <row r="137" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A137" s="119"/>
-      <c r="B137" t="s">
-        <v>317</v>
-      </c>
+      <c r="AX136" s="52"/>
+      <c r="BC136" s="62"/>
+      <c r="BD136" s="31"/>
+      <c r="BE136" s="31"/>
+      <c r="BF136" s="31"/>
+      <c r="BG136" s="62"/>
+      <c r="BH136" s="31"/>
+      <c r="BI136" s="31"/>
+      <c r="BJ136" s="31"/>
+    </row>
+    <row r="137" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A137" s="203"/>
       <c r="D137" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F137" t="s">
-        <v>334</v>
-      </c>
-      <c r="G137" s="51"/>
-      <c r="H137"/>
-      <c r="I137"/>
-      <c r="J137"/>
-      <c r="K137" s="51"/>
-      <c r="L137"/>
-      <c r="M137"/>
-      <c r="N137"/>
-      <c r="O137" s="51"/>
-      <c r="P137"/>
-      <c r="Q137"/>
-      <c r="R137"/>
-      <c r="S137" s="51"/>
-      <c r="T137"/>
-      <c r="U137"/>
-      <c r="V137"/>
-      <c r="W137" s="51"/>
-      <c r="X137"/>
-      <c r="Y137"/>
-      <c r="Z137"/>
-      <c r="AA137" s="51"/>
-      <c r="AB137"/>
-      <c r="AC137"/>
-      <c r="AD137"/>
-      <c r="AE137" s="51"/>
-      <c r="AF137"/>
-      <c r="AG137"/>
-      <c r="AH137"/>
+      <c r="AM137" s="51"/>
+      <c r="AP137" s="52"/>
+      <c r="AQ137" s="51"/>
+      <c r="AT137" s="52"/>
       <c r="AU137" s="51"/>
       <c r="AV137"/>
       <c r="AW137"/>
-      <c r="AX137"/>
-      <c r="BK137" s="51"/>
-      <c r="BL137"/>
-      <c r="BM137"/>
-      <c r="BN137"/>
-    </row>
-    <row r="138" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A138" s="119"/>
-      <c r="B138" t="s">
-        <v>320</v>
-      </c>
+      <c r="AX137" s="52"/>
+      <c r="BC137" s="62"/>
+      <c r="BD137" s="31"/>
+      <c r="BE137" s="31"/>
+      <c r="BF137" s="31"/>
+      <c r="BG137" s="62"/>
+      <c r="BH137" s="31"/>
+      <c r="BI137" s="31"/>
+      <c r="BJ137" s="31"/>
+    </row>
+    <row r="138" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A138" s="203"/>
       <c r="D138" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F138" t="s">
-        <v>335</v>
-      </c>
-      <c r="G138" s="51"/>
-      <c r="H138"/>
-      <c r="I138"/>
-      <c r="J138"/>
-      <c r="K138" s="51"/>
-      <c r="L138"/>
-      <c r="M138"/>
-      <c r="N138"/>
-      <c r="O138" s="51"/>
-      <c r="P138"/>
-      <c r="Q138"/>
-      <c r="R138"/>
-      <c r="S138" s="51"/>
-      <c r="T138"/>
-      <c r="U138"/>
-      <c r="V138"/>
-      <c r="W138" s="51"/>
-      <c r="X138"/>
-      <c r="Y138"/>
-      <c r="Z138"/>
-      <c r="AA138" s="51"/>
-      <c r="AB138"/>
-      <c r="AC138"/>
-      <c r="AD138"/>
-      <c r="AE138" s="51"/>
-      <c r="AF138"/>
-      <c r="AG138"/>
-      <c r="AH138"/>
+      <c r="AM138" s="51"/>
+      <c r="AP138" s="52"/>
+      <c r="AQ138" s="51"/>
+      <c r="AT138" s="52"/>
       <c r="AU138" s="51"/>
       <c r="AV138"/>
       <c r="AW138"/>
-      <c r="AX138"/>
-      <c r="BK138" s="51"/>
-      <c r="BL138"/>
-      <c r="BM138"/>
-      <c r="BN138"/>
-    </row>
-    <row r="139" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A139" s="119"/>
-      <c r="B139" t="s">
-        <v>323</v>
-      </c>
+      <c r="AX138" s="52"/>
+      <c r="BC138" s="62"/>
+      <c r="BD138" s="31"/>
+      <c r="BE138" s="31"/>
+      <c r="BF138" s="31"/>
+      <c r="BG138" s="62"/>
+      <c r="BH138" s="31"/>
+      <c r="BI138" s="31"/>
+      <c r="BJ138" s="31"/>
+    </row>
+    <row r="139" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A139" s="203"/>
       <c r="D139" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="E139" t="s">
-        <v>336</v>
-      </c>
-      <c r="F139" t="s">
-        <v>337</v>
-      </c>
-      <c r="G139" s="51"/>
-      <c r="H139"/>
-      <c r="I139"/>
-      <c r="J139"/>
-      <c r="K139" s="51"/>
-      <c r="L139"/>
-      <c r="M139"/>
-      <c r="N139"/>
-      <c r="O139" s="51"/>
-      <c r="P139"/>
-      <c r="Q139"/>
-      <c r="R139"/>
-      <c r="S139" s="51"/>
-      <c r="T139"/>
-      <c r="U139"/>
-      <c r="V139"/>
-      <c r="W139" s="51"/>
-      <c r="X139"/>
-      <c r="Y139"/>
-      <c r="Z139"/>
-      <c r="AA139" s="51"/>
-      <c r="AB139"/>
-      <c r="AC139"/>
-      <c r="AD139"/>
-      <c r="AE139" s="51"/>
-      <c r="AF139"/>
-      <c r="AG139"/>
-      <c r="AH139"/>
+      <c r="AM139" s="51"/>
+      <c r="AP139" s="52"/>
+      <c r="AQ139" s="51"/>
+      <c r="AT139" s="52"/>
       <c r="AU139" s="51"/>
       <c r="AV139"/>
       <c r="AW139"/>
-      <c r="AX139"/>
-      <c r="BK139" s="51"/>
-      <c r="BL139"/>
-      <c r="BM139"/>
-      <c r="BN139"/>
-    </row>
-    <row r="140" spans="1:66" ht="91.5" x14ac:dyDescent="0.25">
-      <c r="A140" s="119" t="s">
-        <v>280</v>
-      </c>
-      <c r="B140" t="s">
-        <v>326</v>
-      </c>
+      <c r="AX139" s="52"/>
+      <c r="BC139" s="62"/>
+      <c r="BD139" s="31"/>
+      <c r="BE139" s="31"/>
+      <c r="BF139" s="31"/>
+      <c r="BG139" s="62"/>
+      <c r="BH139" s="31"/>
+      <c r="BI139" s="31"/>
+      <c r="BJ139" s="31"/>
+    </row>
+    <row r="140" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A140" s="203"/>
       <c r="D140" s="1">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="F140" t="s">
-        <v>338</v>
-      </c>
-      <c r="G140" s="51"/>
-      <c r="H140"/>
-      <c r="I140"/>
-      <c r="J140"/>
-      <c r="K140" s="51"/>
-      <c r="L140"/>
-      <c r="M140"/>
-      <c r="N140"/>
-      <c r="O140" s="51"/>
-      <c r="P140"/>
-      <c r="Q140"/>
-      <c r="R140"/>
-      <c r="S140" s="51"/>
-      <c r="T140"/>
-      <c r="U140"/>
-      <c r="V140"/>
-      <c r="W140" s="51"/>
-      <c r="X140"/>
-      <c r="Y140"/>
-      <c r="Z140"/>
-      <c r="AA140" s="51"/>
-      <c r="AB140"/>
-      <c r="AC140"/>
-      <c r="AD140"/>
-      <c r="AE140" s="51"/>
-      <c r="AF140"/>
-      <c r="AG140"/>
-      <c r="AH140"/>
+      <c r="AM140" s="51"/>
+      <c r="AP140" s="52"/>
+      <c r="AQ140" s="51"/>
+      <c r="AT140" s="52"/>
       <c r="AU140" s="51"/>
       <c r="AV140"/>
       <c r="AW140"/>
-      <c r="AX140"/>
-      <c r="BK140" s="51"/>
-      <c r="BL140"/>
-      <c r="BM140"/>
-      <c r="BN140"/>
+      <c r="AX140" s="52"/>
+      <c r="BC140" s="62"/>
+      <c r="BD140" s="31"/>
+      <c r="BE140" s="31"/>
+      <c r="BF140" s="31"/>
+      <c r="BG140" s="62"/>
+      <c r="BH140" s="31"/>
+      <c r="BI140" s="31"/>
+      <c r="BJ140" s="31"/>
+    </row>
+    <row r="141" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A141" s="203"/>
+      <c r="D141" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM141" s="51"/>
+      <c r="AP141" s="52"/>
+      <c r="AQ141" s="51"/>
+      <c r="AT141" s="52"/>
+      <c r="AU141" s="51"/>
+      <c r="AV141"/>
+      <c r="AW141"/>
+      <c r="AX141" s="52"/>
+      <c r="BC141" s="62"/>
+      <c r="BD141" s="31"/>
+      <c r="BE141" s="31"/>
+      <c r="BF141" s="31"/>
+      <c r="BG141" s="62"/>
+      <c r="BH141" s="31"/>
+      <c r="BI141" s="31"/>
+      <c r="BJ141" s="31"/>
+    </row>
+    <row r="142" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A142" s="203"/>
+      <c r="D142" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM142" s="51"/>
+      <c r="AP142" s="52"/>
+      <c r="AQ142" s="51"/>
+      <c r="AT142" s="52"/>
+      <c r="AU142" s="51"/>
+      <c r="AV142"/>
+      <c r="AW142"/>
+      <c r="AX142" s="52"/>
+      <c r="BC142" s="62"/>
+      <c r="BD142" s="31"/>
+      <c r="BE142" s="31"/>
+      <c r="BF142" s="31"/>
+      <c r="BG142" s="62"/>
+      <c r="BH142" s="31"/>
+      <c r="BI142" s="31"/>
+      <c r="BJ142" s="31"/>
+    </row>
+    <row r="143" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A143" s="203"/>
+      <c r="D143" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM143" s="51"/>
+      <c r="AP143" s="52"/>
+      <c r="AQ143" s="51"/>
+      <c r="AT143" s="52"/>
+      <c r="AU143" s="51"/>
+      <c r="AV143"/>
+      <c r="AW143"/>
+      <c r="AX143" s="52"/>
+      <c r="BC143" s="62"/>
+      <c r="BD143" s="31"/>
+      <c r="BE143" s="31"/>
+      <c r="BF143" s="31"/>
+      <c r="BG143" s="62"/>
+      <c r="BH143" s="31"/>
+      <c r="BI143" s="31"/>
+      <c r="BJ143" s="31"/>
+    </row>
+    <row r="144" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="A144" s="203"/>
+      <c r="D144" s="1">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="AM144" s="51"/>
+      <c r="AP144" s="52"/>
+      <c r="AQ144" s="51"/>
+      <c r="AT144" s="52"/>
+      <c r="AU144" s="51"/>
+      <c r="AV144"/>
+      <c r="AW144"/>
+      <c r="AX144" s="52"/>
+      <c r="BC144" s="62"/>
+      <c r="BD144" s="31"/>
+      <c r="BE144" s="31"/>
+      <c r="BF144" s="31"/>
+      <c r="BG144" s="62"/>
+      <c r="BH144" s="31"/>
+      <c r="BI144" s="31"/>
+      <c r="BJ144" s="31"/>
+    </row>
+    <row r="145" spans="1:66" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="203"/>
+      <c r="B145" t="s">
+        <v>775</v>
+      </c>
+      <c r="D145" s="1">
+        <f>COUNTIF(G145:AAN145,"✅")+COUNTIF(G145:AAN145,"✔️")</f>
+        <v>9</v>
+      </c>
+      <c r="E145" t="s">
+        <v>306</v>
+      </c>
+      <c r="F145" t="s">
+        <v>307</v>
+      </c>
+      <c r="AM145" s="51"/>
+      <c r="AP145" s="52"/>
+      <c r="AQ145" s="51"/>
+      <c r="AT145" s="52"/>
+      <c r="AU145" s="51"/>
+      <c r="AV145"/>
+      <c r="AW145"/>
+      <c r="AX145" s="52"/>
+      <c r="BC145" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD145" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE145" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG145" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH145" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI145" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK145" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL145" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM145" s="30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A146" s="203"/>
+      <c r="B146" t="s">
+        <v>776</v>
+      </c>
+      <c r="D146" s="1">
+        <f t="shared" ref="D146:D161" si="14">COUNTIF(G146:AAN146,"✅")+COUNTIF(G146:AAN146,"✔️")</f>
+        <v>9</v>
+      </c>
+      <c r="E146" t="s">
+        <v>309</v>
+      </c>
+      <c r="F146" t="s">
+        <v>310</v>
+      </c>
+      <c r="AM146" s="51"/>
+      <c r="AP146" s="52"/>
+      <c r="AQ146" s="51"/>
+      <c r="AT146" s="52"/>
+      <c r="AU146" s="51"/>
+      <c r="AV146"/>
+      <c r="AW146"/>
+      <c r="AX146" s="52"/>
+      <c r="BC146" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD146" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE146" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG146" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH146" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI146" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK146" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL146" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM146" s="30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A147" s="203"/>
+      <c r="B147" t="s">
+        <v>777</v>
+      </c>
+      <c r="D147" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="E147" t="s">
+        <v>312</v>
+      </c>
+      <c r="F147" t="s">
+        <v>313</v>
+      </c>
+      <c r="AM147" s="51"/>
+      <c r="AP147" s="52"/>
+      <c r="AQ147" s="51"/>
+      <c r="AT147" s="52"/>
+      <c r="AU147" s="51"/>
+      <c r="AV147"/>
+      <c r="AW147"/>
+      <c r="AX147" s="52"/>
+      <c r="BC147" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD147" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE147" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG147" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH147" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI147" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK147" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL147" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM147" s="30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A148" s="203"/>
+      <c r="B148" t="s">
+        <v>778</v>
+      </c>
+      <c r="D148" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="E148" t="s">
+        <v>315</v>
+      </c>
+      <c r="F148" t="s">
+        <v>316</v>
+      </c>
+      <c r="AM148" s="51"/>
+      <c r="AP148" s="52"/>
+      <c r="AQ148" s="51"/>
+      <c r="AT148" s="52"/>
+      <c r="AU148" s="51"/>
+      <c r="AV148"/>
+      <c r="AW148"/>
+      <c r="AX148" s="52"/>
+      <c r="BC148" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD148" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE148" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG148" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH148" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI148" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK148" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL148" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM148" s="30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A149" s="203"/>
+      <c r="B149" t="s">
+        <v>779</v>
+      </c>
+      <c r="D149" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="E149" t="s">
+        <v>318</v>
+      </c>
+      <c r="F149" t="s">
+        <v>319</v>
+      </c>
+      <c r="AM149" s="51"/>
+      <c r="AP149" s="52"/>
+      <c r="AQ149" s="51"/>
+      <c r="AT149" s="52"/>
+      <c r="AU149" s="51"/>
+      <c r="AV149"/>
+      <c r="AW149"/>
+      <c r="AX149" s="52"/>
+      <c r="BC149" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD149" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE149" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG149" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH149" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI149" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK149" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL149" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM149" s="30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A150" s="203"/>
+      <c r="B150" t="s">
+        <v>780</v>
+      </c>
+      <c r="D150" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
+        <v>321</v>
+      </c>
+      <c r="F150" t="s">
+        <v>322</v>
+      </c>
+      <c r="G150" s="51"/>
+      <c r="H150"/>
+      <c r="I150"/>
+      <c r="J150"/>
+      <c r="K150" s="51"/>
+      <c r="L150"/>
+      <c r="M150"/>
+      <c r="N150"/>
+      <c r="O150" s="51"/>
+      <c r="P150"/>
+      <c r="Q150"/>
+      <c r="R150"/>
+      <c r="S150" s="51"/>
+      <c r="T150"/>
+      <c r="U150"/>
+      <c r="V150"/>
+      <c r="W150" s="51"/>
+      <c r="X150"/>
+      <c r="Y150"/>
+      <c r="Z150"/>
+      <c r="AA150" s="51"/>
+      <c r="AB150"/>
+      <c r="AC150"/>
+      <c r="AD150"/>
+      <c r="AE150" s="51"/>
+      <c r="AF150"/>
+      <c r="AG150"/>
+      <c r="AH150"/>
+      <c r="AM150" s="51"/>
+      <c r="AP150" s="52"/>
+      <c r="AQ150" s="51"/>
+      <c r="AT150" s="52"/>
+      <c r="AU150" s="51"/>
+      <c r="AV150"/>
+      <c r="AW150"/>
+      <c r="AX150" s="52"/>
+      <c r="BC150" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD150" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE150" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG150" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH150" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI150" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK150" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL150" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM150" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BN150"/>
+    </row>
+    <row r="151" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A151" s="203"/>
+      <c r="B151" t="s">
+        <v>781</v>
+      </c>
+      <c r="D151" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="E151" t="s">
+        <v>324</v>
+      </c>
+      <c r="F151" t="s">
+        <v>325</v>
+      </c>
+      <c r="G151" s="51"/>
+      <c r="H151"/>
+      <c r="I151"/>
+      <c r="J151"/>
+      <c r="K151" s="51"/>
+      <c r="L151"/>
+      <c r="M151"/>
+      <c r="N151"/>
+      <c r="O151" s="51"/>
+      <c r="P151"/>
+      <c r="Q151"/>
+      <c r="R151"/>
+      <c r="S151" s="51"/>
+      <c r="T151"/>
+      <c r="U151"/>
+      <c r="V151"/>
+      <c r="W151" s="51"/>
+      <c r="X151"/>
+      <c r="Y151"/>
+      <c r="Z151"/>
+      <c r="AA151" s="51"/>
+      <c r="AB151"/>
+      <c r="AC151"/>
+      <c r="AD151"/>
+      <c r="AE151" s="51"/>
+      <c r="AF151"/>
+      <c r="AG151"/>
+      <c r="AH151"/>
+      <c r="AM151" s="51"/>
+      <c r="AP151" s="52"/>
+      <c r="AQ151" s="51"/>
+      <c r="AT151" s="52"/>
+      <c r="AU151" s="51"/>
+      <c r="AV151"/>
+      <c r="AW151"/>
+      <c r="AX151" s="52"/>
+      <c r="BC151" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD151" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE151" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG151" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH151" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI151" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK151" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL151" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM151" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BN151"/>
+    </row>
+    <row r="152" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A152" s="203"/>
+      <c r="B152" t="s">
+        <v>782</v>
+      </c>
+      <c r="D152" s="1">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="E152" t="s">
+        <v>327</v>
+      </c>
+      <c r="F152" t="s">
+        <v>328</v>
+      </c>
+      <c r="G152" s="51"/>
+      <c r="H152"/>
+      <c r="I152"/>
+      <c r="J152"/>
+      <c r="K152" s="51"/>
+      <c r="L152"/>
+      <c r="M152"/>
+      <c r="N152"/>
+      <c r="O152" s="51"/>
+      <c r="P152"/>
+      <c r="Q152"/>
+      <c r="R152"/>
+      <c r="S152" s="51"/>
+      <c r="T152"/>
+      <c r="U152"/>
+      <c r="V152"/>
+      <c r="W152" s="51"/>
+      <c r="X152"/>
+      <c r="Y152"/>
+      <c r="Z152"/>
+      <c r="AA152" s="51"/>
+      <c r="AB152"/>
+      <c r="AC152"/>
+      <c r="AD152"/>
+      <c r="AE152" s="51"/>
+      <c r="AF152"/>
+      <c r="AG152"/>
+      <c r="AH152"/>
+      <c r="AM152" s="51"/>
+      <c r="AP152" s="52"/>
+      <c r="AQ152" s="51"/>
+      <c r="AT152" s="52"/>
+      <c r="AU152" s="51"/>
+      <c r="AV152"/>
+      <c r="AW152"/>
+      <c r="AX152" s="52"/>
+      <c r="BC152" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD152" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BE152" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BG152" s="80" t="s">
+        <v>24</v>
+      </c>
+      <c r="BH152" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BI152" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BK152" s="76" t="s">
+        <v>24</v>
+      </c>
+      <c r="BL152" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BM152" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="BN152"/>
+    </row>
+    <row r="153" spans="1:66" s="8" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="203"/>
+      <c r="C153" s="18"/>
+      <c r="D153" s="10"/>
+      <c r="G153" s="50"/>
+      <c r="H153" s="38"/>
+      <c r="I153" s="38"/>
+      <c r="J153" s="38"/>
+      <c r="K153" s="50"/>
+      <c r="L153" s="38"/>
+      <c r="M153" s="38"/>
+      <c r="N153" s="38"/>
+      <c r="O153" s="66"/>
+      <c r="P153" s="33"/>
+      <c r="Q153" s="33"/>
+      <c r="R153" s="33"/>
+      <c r="S153" s="66"/>
+      <c r="T153" s="33"/>
+      <c r="U153" s="33"/>
+      <c r="V153" s="33"/>
+      <c r="W153" s="66"/>
+      <c r="X153" s="33"/>
+      <c r="Y153" s="33"/>
+      <c r="Z153" s="33"/>
+      <c r="AA153" s="66"/>
+      <c r="AB153" s="33"/>
+      <c r="AC153" s="33"/>
+      <c r="AD153" s="33"/>
+      <c r="AE153" s="66"/>
+      <c r="AF153" s="33"/>
+      <c r="AG153" s="33"/>
+      <c r="AH153" s="33"/>
+      <c r="AI153" s="84"/>
+      <c r="AL153" s="83"/>
+      <c r="AU153" s="66"/>
+      <c r="AV153" s="33"/>
+      <c r="AW153" s="33"/>
+      <c r="AX153" s="33"/>
+      <c r="AY153" s="84"/>
+      <c r="BB153" s="83"/>
+      <c r="BK153" s="66"/>
+      <c r="BL153" s="33"/>
+      <c r="BM153" s="33"/>
+      <c r="BN153" s="33"/>
+    </row>
+    <row r="154" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A154" s="203"/>
+      <c r="B154" t="s">
+        <v>305</v>
+      </c>
+      <c r="D154" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F154" t="s">
+        <v>329</v>
+      </c>
+      <c r="G154" s="51"/>
+      <c r="H154"/>
+      <c r="I154"/>
+      <c r="J154"/>
+      <c r="K154" s="51"/>
+      <c r="L154"/>
+      <c r="M154"/>
+      <c r="N154"/>
+      <c r="O154" s="51"/>
+      <c r="P154"/>
+      <c r="Q154"/>
+      <c r="R154"/>
+      <c r="S154" s="51"/>
+      <c r="T154"/>
+      <c r="U154"/>
+      <c r="V154"/>
+      <c r="W154" s="51"/>
+      <c r="X154"/>
+      <c r="Y154"/>
+      <c r="Z154"/>
+      <c r="AA154" s="51"/>
+      <c r="AB154"/>
+      <c r="AC154"/>
+      <c r="AD154"/>
+      <c r="AE154" s="51"/>
+      <c r="AF154"/>
+      <c r="AG154"/>
+      <c r="AH154"/>
+      <c r="AU154" s="51"/>
+      <c r="AV154"/>
+      <c r="AW154"/>
+      <c r="AX154"/>
+      <c r="BK154" s="51"/>
+      <c r="BL154"/>
+      <c r="BM154"/>
+      <c r="BN154"/>
+    </row>
+    <row r="155" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A155" s="203"/>
+      <c r="B155" t="s">
+        <v>308</v>
+      </c>
+      <c r="D155" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="E155" t="s">
+        <v>330</v>
+      </c>
+      <c r="F155" t="s">
+        <v>331</v>
+      </c>
+      <c r="G155" s="51"/>
+      <c r="H155"/>
+      <c r="I155"/>
+      <c r="J155"/>
+      <c r="K155" s="51"/>
+      <c r="L155"/>
+      <c r="M155"/>
+      <c r="N155"/>
+      <c r="O155" s="51"/>
+      <c r="P155"/>
+      <c r="Q155"/>
+      <c r="R155"/>
+      <c r="S155" s="51"/>
+      <c r="T155"/>
+      <c r="U155"/>
+      <c r="V155"/>
+      <c r="W155" s="51"/>
+      <c r="X155"/>
+      <c r="Y155"/>
+      <c r="Z155"/>
+      <c r="AA155" s="51"/>
+      <c r="AB155"/>
+      <c r="AC155"/>
+      <c r="AD155"/>
+      <c r="AE155" s="51"/>
+      <c r="AF155"/>
+      <c r="AG155"/>
+      <c r="AH155"/>
+      <c r="AU155" s="51"/>
+      <c r="AV155"/>
+      <c r="AW155"/>
+      <c r="AX155"/>
+      <c r="BK155" s="51"/>
+      <c r="BL155"/>
+      <c r="BM155"/>
+      <c r="BN155"/>
+    </row>
+    <row r="156" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A156" s="203"/>
+      <c r="B156" t="s">
+        <v>311</v>
+      </c>
+      <c r="D156" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F156" t="s">
+        <v>332</v>
+      </c>
+      <c r="G156" s="51"/>
+      <c r="H156"/>
+      <c r="I156"/>
+      <c r="J156"/>
+      <c r="K156" s="51"/>
+      <c r="L156"/>
+      <c r="M156"/>
+      <c r="N156"/>
+      <c r="O156" s="51"/>
+      <c r="P156"/>
+      <c r="Q156"/>
+      <c r="R156"/>
+      <c r="S156" s="51"/>
+      <c r="T156"/>
+      <c r="U156"/>
+      <c r="V156"/>
+      <c r="W156" s="51"/>
+      <c r="X156"/>
+      <c r="Y156"/>
+      <c r="Z156"/>
+      <c r="AA156" s="51"/>
+      <c r="AB156"/>
+      <c r="AC156"/>
+      <c r="AD156"/>
+      <c r="AE156" s="51"/>
+      <c r="AF156"/>
+      <c r="AG156"/>
+      <c r="AH156"/>
+      <c r="AU156" s="51"/>
+      <c r="AV156"/>
+      <c r="AW156"/>
+      <c r="AX156"/>
+      <c r="BK156" s="51"/>
+      <c r="BL156"/>
+      <c r="BM156"/>
+      <c r="BN156"/>
+    </row>
+    <row r="157" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A157" s="203"/>
+      <c r="B157" t="s">
+        <v>314</v>
+      </c>
+      <c r="D157" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F157" t="s">
+        <v>333</v>
+      </c>
+      <c r="G157" s="51"/>
+      <c r="H157"/>
+      <c r="I157"/>
+      <c r="J157"/>
+      <c r="K157" s="51"/>
+      <c r="L157"/>
+      <c r="M157"/>
+      <c r="N157"/>
+      <c r="O157" s="51"/>
+      <c r="P157"/>
+      <c r="Q157"/>
+      <c r="R157"/>
+      <c r="S157" s="51"/>
+      <c r="T157"/>
+      <c r="U157"/>
+      <c r="V157"/>
+      <c r="W157" s="51"/>
+      <c r="X157"/>
+      <c r="Y157"/>
+      <c r="Z157"/>
+      <c r="AA157" s="51"/>
+      <c r="AB157"/>
+      <c r="AC157"/>
+      <c r="AD157"/>
+      <c r="AE157" s="51"/>
+      <c r="AF157"/>
+      <c r="AG157"/>
+      <c r="AH157"/>
+      <c r="AU157" s="51"/>
+      <c r="AV157"/>
+      <c r="AW157"/>
+      <c r="AX157"/>
+      <c r="BK157" s="51"/>
+      <c r="BL157"/>
+      <c r="BM157"/>
+      <c r="BN157"/>
+    </row>
+    <row r="158" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A158" s="203"/>
+      <c r="B158" t="s">
+        <v>317</v>
+      </c>
+      <c r="D158" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F158" t="s">
+        <v>334</v>
+      </c>
+      <c r="G158" s="51"/>
+      <c r="H158"/>
+      <c r="I158"/>
+      <c r="J158"/>
+      <c r="K158" s="51"/>
+      <c r="L158"/>
+      <c r="M158"/>
+      <c r="N158"/>
+      <c r="O158" s="51"/>
+      <c r="P158"/>
+      <c r="Q158"/>
+      <c r="R158"/>
+      <c r="S158" s="51"/>
+      <c r="T158"/>
+      <c r="U158"/>
+      <c r="V158"/>
+      <c r="W158" s="51"/>
+      <c r="X158"/>
+      <c r="Y158"/>
+      <c r="Z158"/>
+      <c r="AA158" s="51"/>
+      <c r="AB158"/>
+      <c r="AC158"/>
+      <c r="AD158"/>
+      <c r="AE158" s="51"/>
+      <c r="AF158"/>
+      <c r="AG158"/>
+      <c r="AH158"/>
+      <c r="AU158" s="51"/>
+      <c r="AV158"/>
+      <c r="AW158"/>
+      <c r="AX158"/>
+      <c r="BK158" s="51"/>
+      <c r="BL158"/>
+      <c r="BM158"/>
+      <c r="BN158"/>
+    </row>
+    <row r="159" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A159" s="203"/>
+      <c r="B159" t="s">
+        <v>320</v>
+      </c>
+      <c r="D159" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F159" t="s">
+        <v>335</v>
+      </c>
+      <c r="G159" s="51"/>
+      <c r="H159"/>
+      <c r="I159"/>
+      <c r="J159"/>
+      <c r="K159" s="51"/>
+      <c r="L159"/>
+      <c r="M159"/>
+      <c r="N159"/>
+      <c r="O159" s="51"/>
+      <c r="P159"/>
+      <c r="Q159"/>
+      <c r="R159"/>
+      <c r="S159" s="51"/>
+      <c r="T159"/>
+      <c r="U159"/>
+      <c r="V159"/>
+      <c r="W159" s="51"/>
+      <c r="X159"/>
+      <c r="Y159"/>
+      <c r="Z159"/>
+      <c r="AA159" s="51"/>
+      <c r="AB159"/>
+      <c r="AC159"/>
+      <c r="AD159"/>
+      <c r="AE159" s="51"/>
+      <c r="AF159"/>
+      <c r="AG159"/>
+      <c r="AH159"/>
+      <c r="AU159" s="51"/>
+      <c r="AV159"/>
+      <c r="AW159"/>
+      <c r="AX159"/>
+      <c r="BK159" s="51"/>
+      <c r="BL159"/>
+      <c r="BM159"/>
+      <c r="BN159"/>
+    </row>
+    <row r="160" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A160" s="203"/>
+      <c r="B160" t="s">
+        <v>323</v>
+      </c>
+      <c r="D160" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="E160" t="s">
+        <v>336</v>
+      </c>
+      <c r="F160" t="s">
+        <v>337</v>
+      </c>
+      <c r="G160" s="51"/>
+      <c r="H160"/>
+      <c r="I160"/>
+      <c r="J160"/>
+      <c r="K160" s="51"/>
+      <c r="L160"/>
+      <c r="M160"/>
+      <c r="N160"/>
+      <c r="O160" s="51"/>
+      <c r="P160"/>
+      <c r="Q160"/>
+      <c r="R160"/>
+      <c r="S160" s="51"/>
+      <c r="T160"/>
+      <c r="U160"/>
+      <c r="V160"/>
+      <c r="W160" s="51"/>
+      <c r="X160"/>
+      <c r="Y160"/>
+      <c r="Z160"/>
+      <c r="AA160" s="51"/>
+      <c r="AB160"/>
+      <c r="AC160"/>
+      <c r="AD160"/>
+      <c r="AE160" s="51"/>
+      <c r="AF160"/>
+      <c r="AG160"/>
+      <c r="AH160"/>
+      <c r="AU160" s="51"/>
+      <c r="AV160"/>
+      <c r="AW160"/>
+      <c r="AX160"/>
+      <c r="BK160" s="51"/>
+      <c r="BL160"/>
+      <c r="BM160"/>
+      <c r="BN160"/>
+    </row>
+    <row r="161" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A161" s="203"/>
+      <c r="B161" t="s">
+        <v>326</v>
+      </c>
+      <c r="D161" s="1">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="F161" t="s">
+        <v>338</v>
+      </c>
+      <c r="G161" s="51"/>
+      <c r="H161"/>
+      <c r="I161"/>
+      <c r="J161"/>
+      <c r="K161" s="51"/>
+      <c r="L161"/>
+      <c r="M161"/>
+      <c r="N161"/>
+      <c r="O161" s="51"/>
+      <c r="P161"/>
+      <c r="Q161"/>
+      <c r="R161"/>
+      <c r="S161" s="51"/>
+      <c r="T161"/>
+      <c r="U161"/>
+      <c r="V161"/>
+      <c r="W161" s="51"/>
+      <c r="X161"/>
+      <c r="Y161"/>
+      <c r="Z161"/>
+      <c r="AA161" s="51"/>
+      <c r="AB161"/>
+      <c r="AC161"/>
+      <c r="AD161"/>
+      <c r="AE161" s="51"/>
+      <c r="AF161"/>
+      <c r="AG161"/>
+      <c r="AH161"/>
+      <c r="AU161" s="51"/>
+      <c r="AV161"/>
+      <c r="AW161"/>
+      <c r="AX161"/>
+      <c r="BK161" s="51"/>
+      <c r="BL161"/>
+      <c r="BM161"/>
+      <c r="BN161"/>
     </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="BK1:BN1"/>
-    <mergeCell ref="BK8:BN8"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="AM9:BJ9"/>
+  <mergeCells count="45">
+    <mergeCell ref="A117:A161"/>
+    <mergeCell ref="A108:A115"/>
+    <mergeCell ref="AI8:AL8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="AU1:AX1"/>
+    <mergeCell ref="AY1:BB1"/>
+    <mergeCell ref="AQ1:AT1"/>
+    <mergeCell ref="AU8:AX8"/>
+    <mergeCell ref="AY8:BB8"/>
+    <mergeCell ref="AM1:AP1"/>
+    <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="K8:N8"/>
+    <mergeCell ref="G9:V9"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="S1:V1"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="W9:AL9"/>
+    <mergeCell ref="AI1:AL1"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="G10:BJ10"/>
     <mergeCell ref="W1:Z1"/>
     <mergeCell ref="O8:R8"/>
@@ -14748,29 +15314,11 @@
     <mergeCell ref="BG1:BJ1"/>
     <mergeCell ref="BC8:BF8"/>
     <mergeCell ref="BG8:BJ8"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="W9:AL9"/>
-    <mergeCell ref="AI1:AL1"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A108:A115"/>
-    <mergeCell ref="AI8:AL8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="AU1:AX1"/>
-    <mergeCell ref="AY1:BB1"/>
-    <mergeCell ref="AQ1:AT1"/>
-    <mergeCell ref="AU8:AX8"/>
-    <mergeCell ref="AY8:BB8"/>
-    <mergeCell ref="AM1:AP1"/>
-    <mergeCell ref="AM8:AP8"/>
-    <mergeCell ref="K8:N8"/>
-    <mergeCell ref="G9:V9"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="S1:V1"/>
-    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="BK1:BN1"/>
+    <mergeCell ref="BK8:BN8"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="AM9:BJ9"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Spreadsheets/Opponent_Tracker.xlsx
+++ b/Spreadsheets/Opponent_Tracker.xlsx
@@ -3616,6 +3616,24 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3632,77 +3650,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="29" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="35" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3711,73 +3658,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="35" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="24" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3810,9 +3690,129 @@
     <xf numFmtId="0" fontId="3" fillId="26" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Heading 3" xfId="1" builtinId="18"/>
@@ -4236,96 +4236,96 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="182" t="s">
+      <c r="G1" s="168" t="s">
         <v>771</v>
       </c>
-      <c r="H1" s="183"/>
-      <c r="I1" s="183"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="197" t="s">
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="145" t="s">
         <v>770</v>
       </c>
-      <c r="L1" s="198"/>
-      <c r="M1" s="198"/>
-      <c r="N1" s="199"/>
-      <c r="O1" s="172" t="s">
+      <c r="L1" s="146"/>
+      <c r="M1" s="146"/>
+      <c r="N1" s="147"/>
+      <c r="O1" s="157" t="s">
         <v>769</v>
       </c>
-      <c r="P1" s="173"/>
-      <c r="Q1" s="173"/>
-      <c r="R1" s="174"/>
-      <c r="S1" s="200" t="s">
+      <c r="P1" s="158"/>
+      <c r="Q1" s="158"/>
+      <c r="R1" s="159"/>
+      <c r="S1" s="148" t="s">
         <v>768</v>
       </c>
-      <c r="T1" s="201"/>
-      <c r="U1" s="201"/>
-      <c r="V1" s="202"/>
-      <c r="W1" s="139" t="s">
+      <c r="T1" s="149"/>
+      <c r="U1" s="149"/>
+      <c r="V1" s="150"/>
+      <c r="W1" s="173" t="s">
         <v>765</v>
       </c>
-      <c r="X1" s="140"/>
-      <c r="Y1" s="141"/>
-      <c r="Z1" s="142"/>
-      <c r="AA1" s="131" t="s">
+      <c r="X1" s="174"/>
+      <c r="Y1" s="175"/>
+      <c r="Z1" s="176"/>
+      <c r="AA1" s="200" t="s">
         <v>766</v>
       </c>
-      <c r="AB1" s="132"/>
-      <c r="AC1" s="133"/>
-      <c r="AD1" s="134"/>
-      <c r="AE1" s="127" t="s">
+      <c r="AB1" s="201"/>
+      <c r="AC1" s="202"/>
+      <c r="AD1" s="203"/>
+      <c r="AE1" s="196" t="s">
         <v>767</v>
       </c>
-      <c r="AF1" s="128"/>
-      <c r="AG1" s="129"/>
-      <c r="AH1" s="130"/>
-      <c r="AI1" s="176" t="s">
+      <c r="AF1" s="197"/>
+      <c r="AG1" s="198"/>
+      <c r="AH1" s="199"/>
+      <c r="AI1" s="163" t="s">
         <v>858</v>
       </c>
-      <c r="AJ1" s="177"/>
-      <c r="AK1" s="178"/>
-      <c r="AL1" s="179"/>
-      <c r="AM1" s="119" t="s">
+      <c r="AJ1" s="164"/>
+      <c r="AK1" s="165"/>
+      <c r="AL1" s="166"/>
+      <c r="AM1" s="127" t="s">
         <v>859</v>
       </c>
-      <c r="AN1" s="120"/>
-      <c r="AO1" s="121"/>
-      <c r="AP1" s="122"/>
-      <c r="AQ1" s="119" t="s">
+      <c r="AN1" s="128"/>
+      <c r="AO1" s="129"/>
+      <c r="AP1" s="130"/>
+      <c r="AQ1" s="127" t="s">
         <v>860</v>
       </c>
-      <c r="AR1" s="120"/>
-      <c r="AS1" s="121"/>
-      <c r="AT1" s="122"/>
-      <c r="AU1" s="119" t="s">
+      <c r="AR1" s="128"/>
+      <c r="AS1" s="129"/>
+      <c r="AT1" s="130"/>
+      <c r="AU1" s="127" t="s">
         <v>861</v>
       </c>
-      <c r="AV1" s="120"/>
-      <c r="AW1" s="121"/>
-      <c r="AX1" s="122"/>
-      <c r="AY1" s="119" t="s">
+      <c r="AV1" s="128"/>
+      <c r="AW1" s="129"/>
+      <c r="AX1" s="130"/>
+      <c r="AY1" s="127" t="s">
         <v>862</v>
       </c>
-      <c r="AZ1" s="120"/>
-      <c r="BA1" s="121"/>
-      <c r="BB1" s="122"/>
-      <c r="BC1" s="119" t="s">
+      <c r="AZ1" s="128"/>
+      <c r="BA1" s="129"/>
+      <c r="BB1" s="130"/>
+      <c r="BC1" s="127" t="s">
         <v>829</v>
       </c>
-      <c r="BD1" s="120"/>
-      <c r="BE1" s="121"/>
-      <c r="BF1" s="122"/>
-      <c r="BG1" s="119" t="s">
+      <c r="BD1" s="128"/>
+      <c r="BE1" s="129"/>
+      <c r="BF1" s="130"/>
+      <c r="BG1" s="127" t="s">
         <v>830</v>
       </c>
-      <c r="BH1" s="120"/>
-      <c r="BI1" s="121"/>
-      <c r="BJ1" s="122"/>
-      <c r="BK1" s="119" t="s">
+      <c r="BH1" s="128"/>
+      <c r="BI1" s="129"/>
+      <c r="BJ1" s="130"/>
+      <c r="BK1" s="127" t="s">
         <v>831</v>
       </c>
-      <c r="BL1" s="120"/>
-      <c r="BM1" s="121"/>
-      <c r="BN1" s="122"/>
+      <c r="BL1" s="128"/>
+      <c r="BM1" s="129"/>
+      <c r="BN1" s="130"/>
     </row>
     <row r="2" spans="1:66" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="G2" s="39" t="s">
@@ -4510,15 +4510,15 @@
       </c>
     </row>
     <row r="3" spans="1:66" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="180" t="s">
+      <c r="B3" s="167" t="s">
         <v>8</v>
       </c>
       <c r="C3" s="12"/>
-      <c r="D3" s="159" t="s">
+      <c r="D3" s="191" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="148"/>
-      <c r="F3" s="149"/>
+      <c r="E3" s="126"/>
+      <c r="F3" s="152"/>
       <c r="G3" s="40">
         <f t="shared" ref="G3:AP3" si="0">COUNTIF(G11:G58,"✅")</f>
         <v>5</v>
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="4" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="148"/>
+      <c r="B4" s="126"/>
       <c r="C4" s="13"/>
-      <c r="D4" s="159" t="s">
+      <c r="D4" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="148"/>
-      <c r="F4" s="149"/>
+      <c r="E4" s="126"/>
+      <c r="F4" s="152"/>
       <c r="G4" s="40">
         <f t="shared" ref="G4:AP4" si="3">COUNTIF(G11:G58,"✅")+COUNTIF(G11:G58,"✔️")</f>
         <v>5</v>
@@ -5048,15 +5048,15 @@
       <c r="BJ5" s="52"/>
     </row>
     <row r="6" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="150" t="s">
+      <c r="B6" s="182" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="14"/>
-      <c r="D6" s="181" t="s">
+      <c r="D6" s="151" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="148"/>
-      <c r="F6" s="149"/>
+      <c r="E6" s="126"/>
+      <c r="F6" s="152"/>
       <c r="G6" s="43">
         <v>0</v>
       </c>
@@ -5281,13 +5281,13 @@
       </c>
     </row>
     <row r="7" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="148"/>
+      <c r="B7" s="126"/>
       <c r="C7" s="15"/>
-      <c r="D7" s="181" t="s">
+      <c r="D7" s="151" t="s">
         <v>10</v>
       </c>
-      <c r="E7" s="148"/>
-      <c r="F7" s="149"/>
+      <c r="E7" s="126"/>
+      <c r="F7" s="152"/>
       <c r="G7" s="43">
         <v>0</v>
       </c>
@@ -5512,258 +5512,258 @@
       </c>
     </row>
     <row r="8" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="D8" s="147" t="s">
+      <c r="D8" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="148"/>
-      <c r="F8" s="149"/>
-      <c r="G8" s="168">
+      <c r="E8" s="126"/>
+      <c r="F8" s="152"/>
+      <c r="G8" s="153">
         <f>SUM(G3:J3)</f>
         <v>9</v>
       </c>
-      <c r="H8" s="169"/>
-      <c r="I8" s="170"/>
-      <c r="J8" s="171"/>
-      <c r="K8" s="191">
+      <c r="H8" s="154"/>
+      <c r="I8" s="155"/>
+      <c r="J8" s="156"/>
+      <c r="K8" s="139">
         <f>SUM(K3:N3)</f>
         <v>14</v>
       </c>
-      <c r="L8" s="192"/>
-      <c r="M8" s="193"/>
-      <c r="N8" s="194"/>
-      <c r="O8" s="143">
+      <c r="L8" s="140"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="142"/>
+      <c r="O8" s="177">
         <f>SUM(O3:R3)</f>
         <v>14</v>
       </c>
-      <c r="P8" s="144"/>
-      <c r="Q8" s="145"/>
-      <c r="R8" s="146"/>
-      <c r="S8" s="155">
+      <c r="P8" s="178"/>
+      <c r="Q8" s="179"/>
+      <c r="R8" s="180"/>
+      <c r="S8" s="187">
         <f>SUM(S3:V3)</f>
         <v>9</v>
       </c>
-      <c r="T8" s="156"/>
-      <c r="U8" s="157"/>
-      <c r="V8" s="158"/>
-      <c r="W8" s="151">
+      <c r="T8" s="188"/>
+      <c r="U8" s="189"/>
+      <c r="V8" s="190"/>
+      <c r="W8" s="183">
         <f>SUM(W6:Z6)</f>
         <v>22</v>
       </c>
-      <c r="X8" s="152"/>
-      <c r="Y8" s="153"/>
-      <c r="Z8" s="154"/>
-      <c r="AA8" s="164">
+      <c r="X8" s="184"/>
+      <c r="Y8" s="185"/>
+      <c r="Z8" s="186"/>
+      <c r="AA8" s="192">
         <f>SUM(AA6:AD6)</f>
         <v>14</v>
       </c>
-      <c r="AB8" s="165"/>
-      <c r="AC8" s="166"/>
-      <c r="AD8" s="167"/>
-      <c r="AE8" s="123">
+      <c r="AB8" s="193"/>
+      <c r="AC8" s="194"/>
+      <c r="AD8" s="195"/>
+      <c r="AE8" s="131">
         <f>SUM(AE6:AH6)</f>
         <v>12</v>
       </c>
-      <c r="AF8" s="124"/>
-      <c r="AG8" s="125"/>
-      <c r="AH8" s="126"/>
-      <c r="AI8" s="186">
+      <c r="AF8" s="132"/>
+      <c r="AG8" s="133"/>
+      <c r="AH8" s="134"/>
+      <c r="AI8" s="121">
         <f>SUM(AI6:AL6)</f>
         <v>7</v>
       </c>
-      <c r="AJ8" s="187"/>
-      <c r="AK8" s="188"/>
-      <c r="AL8" s="189"/>
-      <c r="AM8" s="160">
+      <c r="AJ8" s="122"/>
+      <c r="AK8" s="123"/>
+      <c r="AL8" s="124"/>
+      <c r="AM8" s="135">
         <f>SUM(AM6:AP6)</f>
         <v>2</v>
       </c>
-      <c r="AN8" s="161"/>
-      <c r="AO8" s="162"/>
-      <c r="AP8" s="163"/>
-      <c r="AQ8" s="160">
+      <c r="AN8" s="136"/>
+      <c r="AO8" s="137"/>
+      <c r="AP8" s="138"/>
+      <c r="AQ8" s="135">
         <f>SUM(AQ6:AT6)</f>
         <v>0</v>
       </c>
-      <c r="AR8" s="161"/>
-      <c r="AS8" s="162"/>
-      <c r="AT8" s="163"/>
-      <c r="AU8" s="123">
+      <c r="AR8" s="136"/>
+      <c r="AS8" s="137"/>
+      <c r="AT8" s="138"/>
+      <c r="AU8" s="131">
         <f>SUM(AU6:AX6)</f>
         <v>0</v>
       </c>
-      <c r="AV8" s="124"/>
-      <c r="AW8" s="125"/>
-      <c r="AX8" s="126"/>
-      <c r="AY8" s="186">
+      <c r="AV8" s="132"/>
+      <c r="AW8" s="133"/>
+      <c r="AX8" s="134"/>
+      <c r="AY8" s="121">
         <f>SUM(AY6:BB6)</f>
         <v>0</v>
       </c>
-      <c r="AZ8" s="187"/>
-      <c r="BA8" s="188"/>
-      <c r="BB8" s="189"/>
-      <c r="BC8" s="160">
+      <c r="AZ8" s="122"/>
+      <c r="BA8" s="123"/>
+      <c r="BB8" s="124"/>
+      <c r="BC8" s="135">
         <f>SUM(BC6:BF6)</f>
         <v>0</v>
       </c>
-      <c r="BD8" s="161"/>
-      <c r="BE8" s="162"/>
-      <c r="BF8" s="163"/>
-      <c r="BG8" s="160">
+      <c r="BD8" s="136"/>
+      <c r="BE8" s="137"/>
+      <c r="BF8" s="138"/>
+      <c r="BG8" s="135">
         <f>SUM(BG6:BJ6)</f>
         <v>0</v>
       </c>
-      <c r="BH8" s="161"/>
-      <c r="BI8" s="162"/>
-      <c r="BJ8" s="163"/>
-      <c r="BK8" s="123">
+      <c r="BH8" s="136"/>
+      <c r="BI8" s="137"/>
+      <c r="BJ8" s="138"/>
+      <c r="BK8" s="131">
         <f>SUM(BK6:BN6)</f>
         <v>0</v>
       </c>
-      <c r="BL8" s="124"/>
-      <c r="BM8" s="125"/>
-      <c r="BN8" s="126"/>
+      <c r="BL8" s="132"/>
+      <c r="BM8" s="133"/>
+      <c r="BN8" s="134"/>
     </row>
     <row r="9" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D9" s="190" t="s">
+      <c r="D9" s="125" t="s">
         <v>13</v>
       </c>
-      <c r="E9" s="148"/>
-      <c r="F9" s="148"/>
-      <c r="G9" s="195">
+      <c r="E9" s="126"/>
+      <c r="F9" s="126"/>
+      <c r="G9" s="143">
         <f>SUM(G8:V8)</f>
         <v>46</v>
       </c>
-      <c r="H9" s="195"/>
-      <c r="I9" s="196"/>
-      <c r="J9" s="196"/>
-      <c r="K9" s="196"/>
-      <c r="L9" s="196"/>
-      <c r="M9" s="196"/>
-      <c r="N9" s="196"/>
-      <c r="O9" s="196"/>
-      <c r="P9" s="196"/>
-      <c r="Q9" s="196"/>
-      <c r="R9" s="196"/>
-      <c r="S9" s="196"/>
-      <c r="T9" s="196"/>
-      <c r="U9" s="196"/>
-      <c r="V9" s="196"/>
-      <c r="W9" s="135">
+      <c r="H9" s="143"/>
+      <c r="I9" s="144"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="144"/>
+      <c r="L9" s="144"/>
+      <c r="M9" s="144"/>
+      <c r="N9" s="144"/>
+      <c r="O9" s="144"/>
+      <c r="P9" s="144"/>
+      <c r="Q9" s="144"/>
+      <c r="R9" s="144"/>
+      <c r="S9" s="144"/>
+      <c r="T9" s="144"/>
+      <c r="U9" s="144"/>
+      <c r="V9" s="144"/>
+      <c r="W9" s="160">
         <f>SUM(W8:AL8)</f>
         <v>55</v>
       </c>
-      <c r="X9" s="136"/>
-      <c r="Y9" s="136"/>
-      <c r="Z9" s="136"/>
-      <c r="AA9" s="136"/>
-      <c r="AB9" s="136"/>
-      <c r="AC9" s="136"/>
-      <c r="AD9" s="136"/>
-      <c r="AE9" s="136"/>
-      <c r="AF9" s="136"/>
-      <c r="AG9" s="136"/>
-      <c r="AH9" s="136"/>
-      <c r="AI9" s="136"/>
-      <c r="AJ9" s="136"/>
-      <c r="AK9" s="136"/>
-      <c r="AL9" s="175"/>
-      <c r="AM9" s="135">
+      <c r="X9" s="161"/>
+      <c r="Y9" s="161"/>
+      <c r="Z9" s="161"/>
+      <c r="AA9" s="161"/>
+      <c r="AB9" s="161"/>
+      <c r="AC9" s="161"/>
+      <c r="AD9" s="161"/>
+      <c r="AE9" s="161"/>
+      <c r="AF9" s="161"/>
+      <c r="AG9" s="161"/>
+      <c r="AH9" s="161"/>
+      <c r="AI9" s="161"/>
+      <c r="AJ9" s="161"/>
+      <c r="AK9" s="161"/>
+      <c r="AL9" s="162"/>
+      <c r="AM9" s="160">
         <f>SUM(AM8:BB8)</f>
         <v>2</v>
       </c>
-      <c r="AN9" s="136"/>
-      <c r="AO9" s="136"/>
-      <c r="AP9" s="136"/>
-      <c r="AQ9" s="136"/>
-      <c r="AR9" s="136"/>
-      <c r="AS9" s="136"/>
-      <c r="AT9" s="136"/>
-      <c r="AU9" s="136"/>
-      <c r="AV9" s="136"/>
-      <c r="AW9" s="136"/>
-      <c r="AX9" s="136"/>
-      <c r="AY9" s="136"/>
-      <c r="AZ9" s="136"/>
-      <c r="BA9" s="136"/>
-      <c r="BB9" s="136"/>
-      <c r="BC9" s="136"/>
-      <c r="BD9" s="136"/>
-      <c r="BE9" s="136"/>
-      <c r="BF9" s="136"/>
-      <c r="BG9" s="136"/>
-      <c r="BH9" s="136"/>
-      <c r="BI9" s="136"/>
-      <c r="BJ9" s="136"/>
+      <c r="AN9" s="161"/>
+      <c r="AO9" s="161"/>
+      <c r="AP9" s="161"/>
+      <c r="AQ9" s="161"/>
+      <c r="AR9" s="161"/>
+      <c r="AS9" s="161"/>
+      <c r="AT9" s="161"/>
+      <c r="AU9" s="161"/>
+      <c r="AV9" s="161"/>
+      <c r="AW9" s="161"/>
+      <c r="AX9" s="161"/>
+      <c r="AY9" s="161"/>
+      <c r="AZ9" s="161"/>
+      <c r="BA9" s="161"/>
+      <c r="BB9" s="161"/>
+      <c r="BC9" s="161"/>
+      <c r="BD9" s="161"/>
+      <c r="BE9" s="161"/>
+      <c r="BF9" s="161"/>
+      <c r="BG9" s="161"/>
+      <c r="BH9" s="161"/>
+      <c r="BI9" s="161"/>
+      <c r="BJ9" s="161"/>
       <c r="BK9" s="117"/>
       <c r="BL9" s="117"/>
       <c r="BM9" s="117"/>
       <c r="BN9" s="117"/>
     </row>
     <row r="10" spans="1:66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D10" s="190" t="s">
+      <c r="D10" s="125" t="s">
         <v>14</v>
       </c>
-      <c r="E10" s="148"/>
-      <c r="F10" s="148"/>
-      <c r="G10" s="137">
+      <c r="E10" s="126"/>
+      <c r="F10" s="126"/>
+      <c r="G10" s="171">
         <f>SUM(G8:BJ8)</f>
         <v>103</v>
       </c>
-      <c r="H10" s="138"/>
-      <c r="I10" s="138"/>
-      <c r="J10" s="138"/>
-      <c r="K10" s="138"/>
-      <c r="L10" s="138"/>
-      <c r="M10" s="138"/>
-      <c r="N10" s="138"/>
-      <c r="O10" s="138"/>
-      <c r="P10" s="138"/>
-      <c r="Q10" s="138"/>
-      <c r="R10" s="138"/>
-      <c r="S10" s="138"/>
-      <c r="T10" s="138"/>
-      <c r="U10" s="138"/>
-      <c r="V10" s="138"/>
-      <c r="W10" s="138"/>
-      <c r="X10" s="138"/>
-      <c r="Y10" s="138"/>
-      <c r="Z10" s="138"/>
-      <c r="AA10" s="138"/>
-      <c r="AB10" s="138"/>
-      <c r="AC10" s="138"/>
-      <c r="AD10" s="138"/>
-      <c r="AE10" s="138"/>
-      <c r="AF10" s="138"/>
-      <c r="AG10" s="138"/>
-      <c r="AH10" s="138"/>
-      <c r="AI10" s="138"/>
-      <c r="AJ10" s="138"/>
-      <c r="AK10" s="138"/>
-      <c r="AL10" s="138"/>
-      <c r="AM10" s="138"/>
-      <c r="AN10" s="138"/>
-      <c r="AO10" s="138"/>
-      <c r="AP10" s="138"/>
-      <c r="AQ10" s="138"/>
-      <c r="AR10" s="138"/>
-      <c r="AS10" s="138"/>
-      <c r="AT10" s="138"/>
-      <c r="AU10" s="138"/>
-      <c r="AV10" s="138"/>
-      <c r="AW10" s="138"/>
-      <c r="AX10" s="138"/>
-      <c r="AY10" s="138"/>
-      <c r="AZ10" s="138"/>
-      <c r="BA10" s="138"/>
-      <c r="BB10" s="138"/>
-      <c r="BC10" s="138"/>
-      <c r="BD10" s="138"/>
-      <c r="BE10" s="138"/>
-      <c r="BF10" s="138"/>
-      <c r="BG10" s="138"/>
-      <c r="BH10" s="138"/>
-      <c r="BI10" s="138"/>
-      <c r="BJ10" s="138"/>
+      <c r="H10" s="172"/>
+      <c r="I10" s="172"/>
+      <c r="J10" s="172"/>
+      <c r="K10" s="172"/>
+      <c r="L10" s="172"/>
+      <c r="M10" s="172"/>
+      <c r="N10" s="172"/>
+      <c r="O10" s="172"/>
+      <c r="P10" s="172"/>
+      <c r="Q10" s="172"/>
+      <c r="R10" s="172"/>
+      <c r="S10" s="172"/>
+      <c r="T10" s="172"/>
+      <c r="U10" s="172"/>
+      <c r="V10" s="172"/>
+      <c r="W10" s="172"/>
+      <c r="X10" s="172"/>
+      <c r="Y10" s="172"/>
+      <c r="Z10" s="172"/>
+      <c r="AA10" s="172"/>
+      <c r="AB10" s="172"/>
+      <c r="AC10" s="172"/>
+      <c r="AD10" s="172"/>
+      <c r="AE10" s="172"/>
+      <c r="AF10" s="172"/>
+      <c r="AG10" s="172"/>
+      <c r="AH10" s="172"/>
+      <c r="AI10" s="172"/>
+      <c r="AJ10" s="172"/>
+      <c r="AK10" s="172"/>
+      <c r="AL10" s="172"/>
+      <c r="AM10" s="172"/>
+      <c r="AN10" s="172"/>
+      <c r="AO10" s="172"/>
+      <c r="AP10" s="172"/>
+      <c r="AQ10" s="172"/>
+      <c r="AR10" s="172"/>
+      <c r="AS10" s="172"/>
+      <c r="AT10" s="172"/>
+      <c r="AU10" s="172"/>
+      <c r="AV10" s="172"/>
+      <c r="AW10" s="172"/>
+      <c r="AX10" s="172"/>
+      <c r="AY10" s="172"/>
+      <c r="AZ10" s="172"/>
+      <c r="BA10" s="172"/>
+      <c r="BB10" s="172"/>
+      <c r="BC10" s="172"/>
+      <c r="BD10" s="172"/>
+      <c r="BE10" s="172"/>
+      <c r="BF10" s="172"/>
+      <c r="BG10" s="172"/>
+      <c r="BH10" s="172"/>
+      <c r="BI10" s="172"/>
+      <c r="BJ10" s="172"/>
       <c r="BK10" s="118"/>
       <c r="BL10" s="118"/>
       <c r="BM10" s="118"/>
@@ -13014,7 +13014,7 @@
       <c r="BN107" s="33"/>
     </row>
     <row r="108" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A108" s="185" t="s">
+      <c r="A108" s="120" t="s">
         <v>774</v>
       </c>
       <c r="B108" t="s">
@@ -13084,7 +13084,7 @@
       <c r="BJ108" s="31"/>
     </row>
     <row r="109" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A109" s="185"/>
+      <c r="A109" s="120"/>
       <c r="B109" t="s">
         <v>284</v>
       </c>
@@ -13152,7 +13152,7 @@
       <c r="BJ109" s="31"/>
     </row>
     <row r="110" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A110" s="185"/>
+      <c r="A110" s="120"/>
       <c r="B110" t="s">
         <v>287</v>
       </c>
@@ -13220,7 +13220,7 @@
       <c r="BJ110" s="31"/>
     </row>
     <row r="111" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A111" s="185"/>
+      <c r="A111" s="120"/>
       <c r="B111" t="s">
         <v>290</v>
       </c>
@@ -13287,7 +13287,7 @@
       <c r="BJ111" s="31"/>
     </row>
     <row r="112" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A112" s="185"/>
+      <c r="A112" s="120"/>
       <c r="B112" t="s">
         <v>293</v>
       </c>
@@ -13354,7 +13354,7 @@
       <c r="BJ112" s="31"/>
     </row>
     <row r="113" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A113" s="185"/>
+      <c r="A113" s="120"/>
       <c r="B113" t="s">
         <v>296</v>
       </c>
@@ -13421,7 +13421,7 @@
       <c r="BJ113" s="31"/>
     </row>
     <row r="114" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A114" s="185"/>
+      <c r="A114" s="120"/>
       <c r="B114" t="s">
         <v>299</v>
       </c>
@@ -13488,7 +13488,7 @@
       <c r="BJ114" s="31"/>
     </row>
     <row r="115" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A115" s="185"/>
+      <c r="A115" s="120"/>
       <c r="B115" t="s">
         <v>302</v>
       </c>
@@ -13600,7 +13600,7 @@
       <c r="BN116" s="33"/>
     </row>
     <row r="117" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A117" s="203" t="s">
+      <c r="A117" s="119" t="s">
         <v>280</v>
       </c>
       <c r="B117" t="s">
@@ -13654,7 +13654,7 @@
       <c r="BJ117" s="31"/>
     </row>
     <row r="118" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A118" s="203"/>
+      <c r="A118" s="119"/>
       <c r="B118" t="s">
         <v>854</v>
       </c>
@@ -13706,7 +13706,7 @@
       <c r="BJ118" s="31"/>
     </row>
     <row r="119" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A119" s="203"/>
+      <c r="A119" s="119"/>
       <c r="B119" t="s">
         <v>856</v>
       </c>
@@ -13760,7 +13760,7 @@
       <c r="BJ119" s="31"/>
     </row>
     <row r="120" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A120" s="203"/>
+      <c r="A120" s="119"/>
       <c r="D120" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13783,7 +13783,7 @@
       <c r="BJ120" s="31"/>
     </row>
     <row r="121" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A121" s="203"/>
+      <c r="A121" s="119"/>
       <c r="D121" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13806,7 +13806,7 @@
       <c r="BJ121" s="31"/>
     </row>
     <row r="122" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A122" s="203"/>
+      <c r="A122" s="119"/>
       <c r="D122" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13829,7 +13829,7 @@
       <c r="BJ122" s="31"/>
     </row>
     <row r="123" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A123" s="203"/>
+      <c r="A123" s="119"/>
       <c r="D123" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13852,7 +13852,7 @@
       <c r="BJ123" s="31"/>
     </row>
     <row r="124" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A124" s="203"/>
+      <c r="A124" s="119"/>
       <c r="D124" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13875,7 +13875,7 @@
       <c r="BJ124" s="31"/>
     </row>
     <row r="125" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A125" s="203"/>
+      <c r="A125" s="119"/>
       <c r="D125" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13898,7 +13898,7 @@
       <c r="BJ125" s="31"/>
     </row>
     <row r="126" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A126" s="203"/>
+      <c r="A126" s="119"/>
       <c r="D126" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13921,7 +13921,7 @@
       <c r="BJ126" s="31"/>
     </row>
     <row r="127" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A127" s="203"/>
+      <c r="A127" s="119"/>
       <c r="D127" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13944,7 +13944,7 @@
       <c r="BJ127" s="31"/>
     </row>
     <row r="128" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A128" s="203"/>
+      <c r="A128" s="119"/>
       <c r="D128" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13967,7 +13967,7 @@
       <c r="BJ128" s="31"/>
     </row>
     <row r="129" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A129" s="203"/>
+      <c r="A129" s="119"/>
       <c r="D129" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -13990,7 +13990,7 @@
       <c r="BJ129" s="31"/>
     </row>
     <row r="130" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A130" s="203"/>
+      <c r="A130" s="119"/>
       <c r="D130" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14013,7 +14013,7 @@
       <c r="BJ130" s="31"/>
     </row>
     <row r="131" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A131" s="203"/>
+      <c r="A131" s="119"/>
       <c r="D131" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14036,7 +14036,7 @@
       <c r="BJ131" s="31"/>
     </row>
     <row r="132" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A132" s="203"/>
+      <c r="A132" s="119"/>
       <c r="D132" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14059,7 +14059,7 @@
       <c r="BJ132" s="31"/>
     </row>
     <row r="133" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A133" s="203"/>
+      <c r="A133" s="119"/>
       <c r="D133" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14082,7 +14082,7 @@
       <c r="BJ133" s="31"/>
     </row>
     <row r="134" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A134" s="203"/>
+      <c r="A134" s="119"/>
       <c r="D134" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14105,7 +14105,7 @@
       <c r="BJ134" s="31"/>
     </row>
     <row r="135" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A135" s="203"/>
+      <c r="A135" s="119"/>
       <c r="D135" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14128,7 +14128,7 @@
       <c r="BJ135" s="31"/>
     </row>
     <row r="136" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A136" s="203"/>
+      <c r="A136" s="119"/>
       <c r="D136" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14151,7 +14151,7 @@
       <c r="BJ136" s="31"/>
     </row>
     <row r="137" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A137" s="203"/>
+      <c r="A137" s="119"/>
       <c r="D137" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14174,7 +14174,7 @@
       <c r="BJ137" s="31"/>
     </row>
     <row r="138" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A138" s="203"/>
+      <c r="A138" s="119"/>
       <c r="D138" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14197,7 +14197,7 @@
       <c r="BJ138" s="31"/>
     </row>
     <row r="139" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A139" s="203"/>
+      <c r="A139" s="119"/>
       <c r="D139" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14220,7 +14220,7 @@
       <c r="BJ139" s="31"/>
     </row>
     <row r="140" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A140" s="203"/>
+      <c r="A140" s="119"/>
       <c r="D140" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14243,7 +14243,7 @@
       <c r="BJ140" s="31"/>
     </row>
     <row r="141" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A141" s="203"/>
+      <c r="A141" s="119"/>
       <c r="D141" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14266,7 +14266,7 @@
       <c r="BJ141" s="31"/>
     </row>
     <row r="142" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A142" s="203"/>
+      <c r="A142" s="119"/>
       <c r="D142" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14289,7 +14289,7 @@
       <c r="BJ142" s="31"/>
     </row>
     <row r="143" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A143" s="203"/>
+      <c r="A143" s="119"/>
       <c r="D143" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14312,7 +14312,7 @@
       <c r="BJ143" s="31"/>
     </row>
     <row r="144" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A144" s="203"/>
+      <c r="A144" s="119"/>
       <c r="D144" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
@@ -14335,7 +14335,7 @@
       <c r="BJ144" s="31"/>
     </row>
     <row r="145" spans="1:66" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="203"/>
+      <c r="A145" s="119"/>
       <c r="B145" t="s">
         <v>775</v>
       </c>
@@ -14386,7 +14386,7 @@
       </c>
     </row>
     <row r="146" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A146" s="203"/>
+      <c r="A146" s="119"/>
       <c r="B146" t="s">
         <v>776</v>
       </c>
@@ -14437,7 +14437,7 @@
       </c>
     </row>
     <row r="147" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A147" s="203"/>
+      <c r="A147" s="119"/>
       <c r="B147" t="s">
         <v>777</v>
       </c>
@@ -14488,7 +14488,7 @@
       </c>
     </row>
     <row r="148" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A148" s="203"/>
+      <c r="A148" s="119"/>
       <c r="B148" t="s">
         <v>778</v>
       </c>
@@ -14539,7 +14539,7 @@
       </c>
     </row>
     <row r="149" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A149" s="203"/>
+      <c r="A149" s="119"/>
       <c r="B149" t="s">
         <v>779</v>
       </c>
@@ -14590,7 +14590,7 @@
       </c>
     </row>
     <row r="150" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A150" s="203"/>
+      <c r="A150" s="119"/>
       <c r="B150" t="s">
         <v>780</v>
       </c>
@@ -14670,7 +14670,7 @@
       <c r="BN150"/>
     </row>
     <row r="151" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A151" s="203"/>
+      <c r="A151" s="119"/>
       <c r="B151" t="s">
         <v>781</v>
       </c>
@@ -14750,7 +14750,7 @@
       <c r="BN151"/>
     </row>
     <row r="152" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A152" s="203"/>
+      <c r="A152" s="119"/>
       <c r="B152" t="s">
         <v>782</v>
       </c>
@@ -14830,7 +14830,7 @@
       <c r="BN152"/>
     </row>
     <row r="153" spans="1:66" s="8" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="203"/>
+      <c r="A153" s="119"/>
       <c r="C153" s="18"/>
       <c r="D153" s="10"/>
       <c r="G153" s="50"/>
@@ -14875,7 +14875,7 @@
       <c r="BN153" s="33"/>
     </row>
     <row r="154" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A154" s="203"/>
+      <c r="A154" s="119"/>
       <c r="B154" t="s">
         <v>305</v>
       </c>
@@ -14924,7 +14924,7 @@
       <c r="BN154"/>
     </row>
     <row r="155" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A155" s="203"/>
+      <c r="A155" s="119"/>
       <c r="B155" t="s">
         <v>308</v>
       </c>
@@ -14976,7 +14976,7 @@
       <c r="BN155"/>
     </row>
     <row r="156" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A156" s="203"/>
+      <c r="A156" s="119"/>
       <c r="B156" t="s">
         <v>311</v>
       </c>
@@ -15025,7 +15025,7 @@
       <c r="BN156"/>
     </row>
     <row r="157" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A157" s="203"/>
+      <c r="A157" s="119"/>
       <c r="B157" t="s">
         <v>314</v>
       </c>
@@ -15074,7 +15074,7 @@
       <c r="BN157"/>
     </row>
     <row r="158" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A158" s="203"/>
+      <c r="A158" s="119"/>
       <c r="B158" t="s">
         <v>317</v>
       </c>
@@ -15123,7 +15123,7 @@
       <c r="BN158"/>
     </row>
     <row r="159" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A159" s="203"/>
+      <c r="A159" s="119"/>
       <c r="B159" t="s">
         <v>320</v>
       </c>
@@ -15172,7 +15172,7 @@
       <c r="BN159"/>
     </row>
     <row r="160" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A160" s="203"/>
+      <c r="A160" s="119"/>
       <c r="B160" t="s">
         <v>323</v>
       </c>
@@ -15224,7 +15224,7 @@
       <c r="BN160"/>
     </row>
     <row r="161" spans="1:66" x14ac:dyDescent="0.25">
-      <c r="A161" s="203"/>
+      <c r="A161" s="119"/>
       <c r="B161" t="s">
         <v>326</v>
       </c>
@@ -15274,17 +15274,40 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A117:A161"/>
-    <mergeCell ref="A108:A115"/>
-    <mergeCell ref="AI8:AL8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="AU1:AX1"/>
+    <mergeCell ref="BK1:BN1"/>
+    <mergeCell ref="BK8:BN8"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AA1:AD1"/>
+    <mergeCell ref="AM9:BJ9"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="W8:Z8"/>
+    <mergeCell ref="S8:V8"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="D3:F3"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="G10:BJ10"/>
+    <mergeCell ref="W1:Z1"/>
+    <mergeCell ref="O8:R8"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="AQ8:AT8"/>
+    <mergeCell ref="AE8:AH8"/>
+    <mergeCell ref="AA8:AD8"/>
+    <mergeCell ref="BC1:BF1"/>
+    <mergeCell ref="BG1:BJ1"/>
+    <mergeCell ref="BC8:BF8"/>
+    <mergeCell ref="BG8:BJ8"/>
     <mergeCell ref="AY1:BB1"/>
     <mergeCell ref="AQ1:AT1"/>
     <mergeCell ref="AU8:AX8"/>
     <mergeCell ref="AY8:BB8"/>
     <mergeCell ref="AM1:AP1"/>
     <mergeCell ref="AM8:AP8"/>
+    <mergeCell ref="A117:A161"/>
+    <mergeCell ref="A108:A115"/>
+    <mergeCell ref="AI8:AL8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="AU1:AX1"/>
     <mergeCell ref="K8:N8"/>
     <mergeCell ref="G9:V9"/>
     <mergeCell ref="D10:F10"/>
@@ -15296,29 +15319,6 @@
     <mergeCell ref="W9:AL9"/>
     <mergeCell ref="AI1:AL1"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="G10:BJ10"/>
-    <mergeCell ref="W1:Z1"/>
-    <mergeCell ref="O8:R8"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="W8:Z8"/>
-    <mergeCell ref="S8:V8"/>
-    <mergeCell ref="D4:F4"/>
-    <mergeCell ref="D3:F3"/>
-    <mergeCell ref="AQ8:AT8"/>
-    <mergeCell ref="AE8:AH8"/>
-    <mergeCell ref="AA8:AD8"/>
-    <mergeCell ref="BC1:BF1"/>
-    <mergeCell ref="BG1:BJ1"/>
-    <mergeCell ref="BC8:BF8"/>
-    <mergeCell ref="BG8:BJ8"/>
-    <mergeCell ref="BK1:BN1"/>
-    <mergeCell ref="BK8:BN8"/>
-    <mergeCell ref="AE1:AH1"/>
-    <mergeCell ref="AA1:AD1"/>
-    <mergeCell ref="AM9:BJ9"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Spreadsheets/Opponent_Tracker.xlsx
+++ b/Spreadsheets/Opponent_Tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Pokemon TCG Legacy\Spreadsheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6FDD5FE-BEB5-4517-971D-9C9269848DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8092C0C7-F719-4DC8-8CD0-0A313EF3C7CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14715" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="opponents_table" sheetId="1" r:id="rId1"/>
@@ -2622,9 +2622,6 @@
     <t>Spectator Pete</t>
   </si>
   <si>
-    <t>Deck Eruption</t>
-  </si>
-  <si>
     <t>CELESTE HARBOUR
 VERDANT FOREST
 8</t>
@@ -2648,6 +2645,9 @@
     <t>VERDANT FOREST
 GYM PLAZA
 12</t>
+  </si>
+  <si>
+    <t>REPLACE ME</t>
   </si>
 </sst>
 </file>
@@ -4279,31 +4279,31 @@
       <c r="AG1" s="198"/>
       <c r="AH1" s="199"/>
       <c r="AI1" s="163" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AJ1" s="164"/>
       <c r="AK1" s="165"/>
       <c r="AL1" s="166"/>
       <c r="AM1" s="127" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AN1" s="128"/>
       <c r="AO1" s="129"/>
       <c r="AP1" s="130"/>
       <c r="AQ1" s="127" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AR1" s="128"/>
       <c r="AS1" s="129"/>
       <c r="AT1" s="130"/>
       <c r="AU1" s="127" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AV1" s="128"/>
       <c r="AW1" s="129"/>
       <c r="AX1" s="130"/>
       <c r="AY1" s="127" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="AZ1" s="128"/>
       <c r="BA1" s="129"/>
@@ -13718,7 +13718,7 @@
         <v>8</v>
       </c>
       <c r="E119" t="s">
-        <v>857</v>
+        <v>862</v>
       </c>
       <c r="AM119" s="51"/>
       <c r="AO119" s="30" t="s">
